--- a/out/multi_agent_risk_taxonomy.xlsx
+++ b/out/multi_agent_risk_taxonomy.xlsx
@@ -16,9 +16,9 @@
     <sheet name="Notes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Risk Index'!$A$1:$H$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FM-RF Links'!$A$1:$P$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Taxonomy'!$A$1:$L$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Risk Index'!$A$1:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FM-RF Links'!$A$1:$Q$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Taxonomy'!$A$1:$M$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Instances'!$A$1:$K$34</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Evidence'!$A$1:$X$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Sources'!$A$1:$D$31</definedName>
@@ -564,7 +564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -572,9 +572,10 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -605,17 +606,22 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>case_studies</t>
+          <t>evidence</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>evidence_n</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>associations</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>case_study_link</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>evidence_link</t>
         </is>
       </c>
     </row>
@@ -641,26 +647,33 @@
         </is>
       </c>
       <c r="E2" s="3">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$B$2:$B$90,"Case study")/10</f>
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*")/10</f>
         <v/>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>CS1</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+          <t>CS1, AIV-07, AIV-06, AIV-04, AIV-01, AIV-02</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Information Asymmetries
+Network Effects
 Selection Pressures
-Destabilising Dynamics</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
+Destabilising Dynamics
+Commitment and Trust</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
         <is>
           <t>TRUE
 TRUE
-FALSE</t>
+TRUE
+FALSE
+TRUE</t>
         </is>
       </c>
     </row>
@@ -686,7 +699,7 @@
         </is>
       </c>
       <c r="E3" s="3">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$B$2:$B$90,"Case study")/10</f>
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*")/10</f>
         <v/>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -694,7 +707,10 @@
           <t>CS2, CS3, CS6, CS9, CS11</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Information Asymmetries
 Selection Pressures
@@ -703,7 +719,7 @@
 Multi-Agent Security</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="I3" s="4" t="inlineStr">
         <is>
           <t>TRUE
 TRUE
@@ -735,15 +751,18 @@
         </is>
       </c>
       <c r="E4" s="3">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*",Evidence!$B$2:$B$90,"Case study")/10</f>
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*")/10</f>
         <v/>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>CS4, CS5</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+          <t>CS4, CS5, AIR-2026-0183, LW-01, LW-02, AIR-2026-0219</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Network Effects
 Selection Pressures
@@ -751,9 +770,9 @@
 Multi-Agent Security</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>FALSE
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>TRUE
 TRUE
 TRUE
 TRUE</t>
@@ -782,21 +801,24 @@
         </is>
       </c>
       <c r="E5" s="6">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Information Asymmetries*",Evidence!$B$2:$B$90,"Case study")/10</f>
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Information Asymmetries*")/10</f>
         <v/>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>CS1, CS6, CS7</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
+          <t>CS1, CS6, CS7, AIV-07, AIV-06, AIV-05, AIR-2025-0149, AIV-03, AIV-01, AIV-02</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Miscoordination
 Conflict</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>TRUE
 TRUE</t>
@@ -825,22 +847,27 @@
         </is>
       </c>
       <c r="E6" s="6">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Network Effects*",Evidence!$B$2:$B$90,"Case study")/10</f>
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Network Effects*")/10</f>
         <v/>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>CS7, CS8, CS10</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>Collusion</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>FALSE</t>
+          <t>CS7, CS8, CS10, AIV-07, AIR-2026-0193, AIR-2026-0189, LW-01, LW-05, AIV-03, AIR-2025-0068, AIV-01</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>Miscoordination
+Collusion</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="inlineStr">
+        <is>
+          <t>TRUE
+TRUE</t>
         </is>
       </c>
     </row>
@@ -866,7 +893,7 @@
         </is>
       </c>
       <c r="E7" s="6">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Selection Pressures*",Evidence!$B$2:$B$90,"Case study")/10</f>
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Selection Pressures*")/10</f>
         <v/>
       </c>
       <c r="F7" s="5" t="inlineStr">
@@ -874,14 +901,17 @@
           <t>CS1, CS2, CS4, CS9</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Miscoordination
 Conflict
 Collusion</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>TRUE
 TRUE
@@ -911,7 +941,7 @@
         </is>
       </c>
       <c r="E8" s="6">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Destabilising Dynamics*",Evidence!$B$2:$B$90,"Case study")/10</f>
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Destabilising Dynamics*")/10</f>
         <v/>
       </c>
       <c r="F8" s="5" t="inlineStr">
@@ -919,13 +949,16 @@
           <t>CS3, CS10</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Miscoordination
 Conflict</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>FALSE
 TRUE</t>
@@ -954,22 +987,27 @@
         </is>
       </c>
       <c r="E9" s="6">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Commitment and Trust*",Evidence!$B$2:$B$90,"Case study")/10</f>
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Commitment and Trust*")/10</f>
         <v/>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>CS2, CS9, CS11</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>Conflict</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>CS2, CS9, CS11, AIR-2026-0180, AIV-06, AIR-2026-0101, AIV-05, AIR-2025-0177, AIR-2025-0136</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Miscoordination
+Conflict</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="inlineStr">
+        <is>
+          <t>TRUE
+TRUE</t>
         </is>
       </c>
     </row>
@@ -995,20 +1033,23 @@
         </is>
       </c>
       <c r="E10" s="6">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Emergent Agency*",Evidence!$B$2:$B$90,"Case study")/10</f>
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Emergent Agency*")/10</f>
         <v/>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>CS4, CS12</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr">
+          <t>CS4, CS12, AIR-2026-0183, LW-01, AIR-2026-0219, LW-05, AIR-2025-0027, AIR-2025-0019</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Collusion</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
@@ -1036,21 +1077,24 @@
         </is>
       </c>
       <c r="E11" s="6">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Multi-Agent Security*",Evidence!$B$2:$B$90,"Case study")/10</f>
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Multi-Agent Security*")/10</f>
         <v/>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>CS5, CS8, CS12, CS13</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
+          <t>CS5, CS8, CS12, CS13, AIR-2026-0193, AIR-2026-0189, AIR-2026-0183, AIR-2026-0180, LW-01, AIR-2026-0194, LW-02, AIR-2026-0219, AIR-2026-0101, AIR-2026-0029, AIR-2025-0177, AIR-2025-0149, AIR-2025-0136, AIR-2025-0070, AIR-2025-0068, AIR-2025-0019</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Conflict
 Collusion</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>FALSE
 TRUE</t>
@@ -1060,22 +1104,22 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>grounding_score = highest evidence_score / 10 among case studies tagged with this risk (Hammond et al. 2025, Table 3).</t>
+          <t>grounding_score = highest evidence_score / 10 across every piece of evidence tagged with this risk: Hammond et al. 2025 case studies and inventory incidents alike. evidence lists their ids, evidence_n counts them.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>associations = linked risk factors (for a failure mode) or failure modes (for a risk factor). case_study_link is line-aligned: TRUE if a case study is tagged with both ends, FALSE if the paper links them only in the text.</t>
+          <t>associations = linked risk factors (for a failure mode) or failure modes (for a risk factor). evidence_link is line-aligned: TRUE if a piece of evidence is tagged with both ends, FALSE if the paper links them only in the text.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H11"/>
+  <autoFilter ref="A1:I11"/>
   <mergeCells count="2">
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="A14:I14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1087,7 +1131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1099,13 +1143,14 @@
     <col width="34" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
     <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-    <col width="44" customWidth="1" min="16" max="16"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="44" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1126,7 +1171,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>case_study_link</t>
+          <t>evidence_link</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -1156,35 +1201,40 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>case_studies_tagged_both</t>
+          <t>evidence_tagged_both</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>hammond_type</t>
+          <t>evidence_n</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>source_class</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>type</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>evidence_strength_max</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>evidence_score_max</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>case_study_source</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>evidence_source</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>text_reference</t>
         </is>
@@ -1211,7 +1261,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Case study + text</t>
+          <t>Evidence + text</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1245,33 +1295,52 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>CS1: Zero-Shot Coordination Failures in Driving</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Novel experiment by report authors</t>
-        </is>
+          <t>CS1: Zero-Shot Coordination Failures in Driving
+AIV-07: DeepSeek-V3.2 persuasion campaign: invented a self-serving metric; the group ad…
+AIV-06: Agents finetune their own leader: Opus assumed GPT-5.5 agreed without confirmin…
+AIV-01: Hallucinated mailing list spreads between agents: o3 invented a 93-person maili…
+AIV-02: False 'broken UI' belief spreads: Gemini 2.5 Pro logged its own misclicks as sy…</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Synthetic evidence</t>
-        </is>
-      </c>
-      <c r="M2" s="2">
-        <f>IF(N2=0,"—",IF(N2&gt;=9,"Strong",IF(N2&gt;=6,"Moderate",IF(N2&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="N2" s="4">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$K$2:$K$90,"*Information Asymmetries*",Evidence!$B$2:$B$90,"Case study")</f>
-        <v/>
-      </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>Report authors (App. B.1)</t>
-        </is>
+          <t>Novel experiment by report authors
+Operator blog
+Operator blog
+Operator blog
+Operator blog</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic evidence
+Synthetic evidence
+Synthetic evidence
+Synthetic evidence
+Synthetic evidence</t>
+        </is>
+      </c>
+      <c r="N2" s="2">
+        <f>IF(O2=0,"—",IF(O2&gt;=9,"Strong",IF(O2&gt;=6,"Moderate",IF(O2&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="O2" s="4">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$K$2:$K$90,"*Information Asymmetries*")</f>
+        <v/>
       </c>
       <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Report authors (App. B.1)
+Persuasion in the AI Village: DeepSeek-V3.2 &amp; Gemini 2.5 Pro
+AIs finetune their own leader: a barking simpleton
+Season 2 recap: the story of the world's first AI-organized event
+What did we learn from the AI Village in 2025?</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>info asymmetries can cause miscoordination (§1.1, §3); Credit Assignment &amp; Communication Constraints cross-ref §2.1/§3.1.</t>
         </is>
@@ -1288,7 +1357,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Selection Pressures</t>
+          <t>Network Effects</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
@@ -1298,7 +1367,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Case study</t>
+          <t>Evidence</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1317,12 +1386,105 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
+          <t>Error Propagation
+Network Rewiring
+Homogeneity and Correlated Failures</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Evaluating and Monitoring Networks
+Faithful and Tractable Simulations
+Improving Network Security and Stability</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>AIV-07: DeepSeek-V3.2 persuasion campaign: invented a self-serving metric; the group ad…
+AIV-01: Hallucinated mailing list spreads between agents: o3 invented a 93-person maili…</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Operator blog
+Operator blog</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic evidence
+Synthetic evidence</t>
+        </is>
+      </c>
+      <c r="N3" s="2">
+        <f>IF(O3=0,"—",IF(O3&gt;=9,"Strong",IF(O3&gt;=6,"Moderate",IF(O3&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="O3" s="4">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$K$2:$K$90,"*Network Effects*")</f>
+        <v/>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Persuasion in the AI Village: DeepSeek-V3.2 &amp; Gemini 2.5 Pro
+Season 2 recap: the story of the world's first AI-organized event</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Miscoordination</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Selection Pressures</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Incompatible Strategies
+Credit Assignment
+Limited Interactions</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Communication
+Norms and Conventions
+Modelling Other Agents</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>Undesirable Dispositions from Competition
 Undesirable Dispositions from Human Data
 Undesirable Capabilities</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>Evaluating Against Diverse Co-Players
 Environment Design
@@ -1331,79 +1493,82 @@
 Simulating Selection Pressures</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>CS1: Zero-Shot Coordination Failures in Driving</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Novel experiment by report authors</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Synthetic evidence</t>
         </is>
       </c>
-      <c r="M3" s="2">
-        <f>IF(N3=0,"—",IF(N3&gt;=9,"Strong",IF(N3&gt;=6,"Moderate",IF(N3&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="N3" s="4">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$K$2:$K$90,"*Selection Pressures*",Evidence!$B$2:$B$90,"Case study")</f>
-        <v/>
-      </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="N4" s="2">
+        <f>IF(O4=0,"—",IF(O4&gt;=9,"Strong",IF(O4&gt;=6,"Moderate",IF(O4&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="O4" s="4">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$K$2:$K$90,"*Selection Pressures*")</f>
+        <v/>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Report authors (App. B.1)</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Miscoordination</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>Destabilising Dynamics</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Text cross-reference only</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Incompatible Strategies
 Credit Assignment
 Limited Interactions</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Communication
 Norms and Conventions
 Modelling Other Agents</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Feedback Loops
 Cyclic Behaviour
@@ -1412,79 +1577,173 @@
 Distributional Shift</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>Understanding Dynamics
 Monitoring and Stabilising Dynamics
 Regulating Adaptive Multi-Agent Systems</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M4" s="2">
-        <f>IF(N4=0,"—",IF(N4&gt;=9,"Strong",IF(N4&gt;=6,"Moderate",IF(N4&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="N4" s="4">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$K$2:$K$90,"*Destabilising Dynamics*",Evidence!$B$2:$B$90,"Case study")</f>
-        <v/>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="N5" s="2">
+        <f>IF(O5=0,"—",IF(O5&gt;=9,"Strong",IF(O5&gt;=6,"Moderate",IF(O5&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="O5" s="4">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$K$2:$K$90,"*Destabilising Dynamics*")</f>
+        <v/>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>Credit Assignment cross-refs §3.4 (distributional shift).</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="9" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Miscoordination</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Commitment and Trust</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Incompatible Strategies
+Credit Assignment
+Limited Interactions</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Communication
+Norms and Conventions
+Modelling Other Agents</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Inefficient Outcomes
+Threats and Extortion
+Rigidity and Mistaken Commitments</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Keeping Humans in the Loop
+Limiting Commitment Power
+Institutions and Normative Infrastructure
+Privacy-Preserving Monitoring
+Mutual Simulation and Transparency</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>AIV-06: Agents finetune their own leader: Opus assumed GPT-5.5 agreed without confirmin…</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Operator blog</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic evidence</t>
+        </is>
+      </c>
+      <c r="N6" s="2">
+        <f>IF(O6=0,"—",IF(O6&gt;=9,"Strong",IF(O6&gt;=6,"Moderate",IF(O6&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="O6" s="4">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$K$2:$K$90,"*Commitment and Trust*")</f>
+        <v/>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>AIs finetune their own leader: a barking simpleton</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Information Asymmetries</t>
         </is>
       </c>
-      <c r="D5" s="10" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>Case study + text</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Evidence + text</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t>Social Dilemmas
 Military Domains
 Coercion and Extortion</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>Learning Peer and Pool Incentivisation
 Establishing Trust
@@ -1494,14 +1753,14 @@
 Evidential Reasoning</t>
         </is>
       </c>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Communication Constraints
 Bargaining
 Deception</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Information Design
 Individual Information Revelation
@@ -1509,72 +1768,75 @@
 Truthful AI</t>
         </is>
       </c>
-      <c r="J5" s="9" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>CS6: AI Agents Can Learn to Manipulate Financial Markets</t>
         </is>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="K7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>Literature</t>
         </is>
       </c>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>Synthetic evidence</t>
         </is>
       </c>
-      <c r="M5" s="9">
-        <f>IF(N5=0,"—",IF(N5&gt;=9,"Strong",IF(N5&gt;=6,"Moderate",IF(N5&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="N5" s="10">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Information Asymmetries*",Evidence!$B$2:$B$90,"Case study")</f>
-        <v/>
-      </c>
-      <c r="O5" s="9" t="inlineStr">
+      <c r="N7" s="9">
+        <f>IF(O7=0,"—",IF(O7&gt;=9,"Strong",IF(O7&gt;=6,"Moderate",IF(O7&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="O7" s="10">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Information Asymmetries*")</f>
+        <v/>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
         <is>
           <t>Shearer et al. (2023); Wang &amp; Wellman (2020)</t>
         </is>
       </c>
-      <c r="P5" s="9" t="inlineStr">
+      <c r="Q7" s="9" t="inlineStr">
         <is>
           <t>Bargaining under asymmetric info → costly conflict (§3.1).</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Selection Pressures</t>
         </is>
       </c>
-      <c r="D6" s="10" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>Case study + text</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Evidence + text</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t>Social Dilemmas
 Military Domains
 Coercion and Extortion</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G8" s="9" t="inlineStr">
         <is>
           <t>Learning Peer and Pool Incentivisation
 Establishing Trust
@@ -1584,14 +1846,14 @@
 Evidential Reasoning</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>Undesirable Dispositions from Competition
 Undesirable Dispositions from Human Data
 Undesirable Capabilities</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>Evaluating Against Diverse Co-Players
 Environment Design
@@ -1600,76 +1862,79 @@
 Simulating Selection Pressures</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>CS2: Common Resource Problems
 CS9: Cooperation Fails to Culturally Evolve among LLM Agents</t>
         </is>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="K8" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>Literature
 Literature</t>
         </is>
       </c>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>Synthetic evidence
 Synthetic evidence</t>
         </is>
       </c>
-      <c r="M6" s="9">
-        <f>IF(N6=0,"—",IF(N6&gt;=9,"Strong",IF(N6&gt;=6,"Moderate",IF(N6&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="N6" s="10">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Selection Pressures*",Evidence!$B$2:$B$90,"Case study")</f>
-        <v/>
-      </c>
-      <c r="O6" s="9" t="inlineStr">
+      <c r="N8" s="9">
+        <f>IF(O8=0,"—",IF(O8&gt;=9,"Strong",IF(O8&gt;=6,"Moderate",IF(O8&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="O8" s="10">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Selection Pressures*")</f>
+        <v/>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
         <is>
           <t>Piatti et al. (2024), GovSim
 Vallinder &amp; Hughes (2024)</t>
         </is>
       </c>
-      <c r="P6" s="9" t="inlineStr">
+      <c r="Q8" s="9" t="inlineStr">
         <is>
           <t>Cooperative Dispositions direction cross-refs §3.3 (conflict-prone dispositions from data/training).</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Destabilising Dynamics</t>
         </is>
       </c>
-      <c r="D7" s="10" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Case study + text</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>Evidence + text</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t>Social Dilemmas
 Military Domains
 Coercion and Extortion</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G9" s="9" t="inlineStr">
         <is>
           <t>Learning Peer and Pool Incentivisation
 Establishing Trust
@@ -1679,7 +1944,7 @@
 Evidential Reasoning</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>Feedback Loops
 Cyclic Behaviour
@@ -1688,79 +1953,82 @@
 Distributional Shift</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Understanding Dynamics
 Monitoring and Stabilising Dynamics
 Regulating Adaptive Multi-Agent Systems</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>CS3: Escalation in Military Conflicts</t>
         </is>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="K9" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>Literature</t>
         </is>
       </c>
-      <c r="L7" s="9" t="inlineStr">
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>Synthetic evidence</t>
         </is>
       </c>
-      <c r="M7" s="9">
-        <f>IF(N7=0,"—",IF(N7&gt;=9,"Strong",IF(N7&gt;=6,"Moderate",IF(N7&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="N7" s="10">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Destabilising Dynamics*",Evidence!$B$2:$B$90,"Case study")</f>
-        <v/>
-      </c>
-      <c r="O7" s="9" t="inlineStr">
+      <c r="N9" s="9">
+        <f>IF(O9=0,"—",IF(O9&gt;=9,"Strong",IF(O9&gt;=6,"Moderate",IF(O9&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="O9" s="10">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Destabilising Dynamics*")</f>
+        <v/>
+      </c>
+      <c r="P9" s="9" t="inlineStr">
         <is>
           <t>Rivera et al. (2024)</t>
         </is>
       </c>
-      <c r="P7" s="9" t="inlineStr">
+      <c r="Q9" s="9" t="inlineStr">
         <is>
           <t>conflicts can escalate via destabilising dynamics (§3 intro).</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>Commitment and Trust</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Case study + text</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Evidence + text</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t>Social Dilemmas
 Military Domains
 Coercion and Extortion</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="G10" s="9" t="inlineStr">
         <is>
           <t>Learning Peer and Pool Incentivisation
 Establishing Trust
@@ -1770,14 +2038,14 @@
 Evidential Reasoning</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>Inefficient Outcomes
 Threats and Extortion
 Rigidity and Mistaken Commitments</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>Keeping Humans in the Loop
 Limiting Commitment Power
@@ -1786,80 +2054,83 @@
 Mutual Simulation and Transparency</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>CS2: Common Resource Problems
 CS9: Cooperation Fails to Culturally Evolve among LLM Agents
 CS11: Dead Hands and Automated Deterrence</t>
         </is>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="K10" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" s="9" t="inlineStr">
         <is>
           <t>Literature
 Literature
 Historical example</t>
         </is>
       </c>
-      <c r="L8" s="9" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>Synthetic evidence
 Synthetic evidence
 Observed in real world</t>
         </is>
       </c>
-      <c r="M8" s="9">
-        <f>IF(N8=0,"—",IF(N8&gt;=9,"Strong",IF(N8&gt;=6,"Moderate",IF(N8&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="N8" s="10">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Commitment and Trust*",Evidence!$B$2:$B$90,"Case study")</f>
-        <v/>
-      </c>
-      <c r="O8" s="9" t="inlineStr">
+      <c r="N10" s="9">
+        <f>IF(O10=0,"—",IF(O10&gt;=9,"Strong",IF(O10&gt;=6,"Moderate",IF(O10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="O10" s="10">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Commitment and Trust*")</f>
+        <v/>
+      </c>
+      <c r="P10" s="9" t="inlineStr">
         <is>
           <t>Piatti et al. (2024), GovSim
 Vallinder &amp; Hughes (2024)
 Hoffman (2009); Talbot (2005)</t>
         </is>
       </c>
-      <c r="P8" s="9" t="inlineStr">
+      <c r="Q10" s="9" t="inlineStr">
         <is>
           <t>Establishing Trust direction cross-refs §3.5; inability to commit is a major cause of costly conflict.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Multi-Agent Security</t>
         </is>
       </c>
-      <c r="D9" s="10" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Text cross-reference only</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t>Social Dilemmas
 Military Domains
 Coercion and Extortion</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G11" s="9" t="inlineStr">
         <is>
           <t>Learning Peer and Pool Incentivisation
 Establishing Trust
@@ -1869,7 +2140,7 @@
 Evidential Reasoning</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>Swarm Attacks
 Heterogeneous Attacks
@@ -1879,7 +2150,7 @@
 Undetectable Threats</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>Secure Interaction Protocols
 Monitoring and Threat Detection
@@ -1887,170 +2158,176 @@
 Sociotechnical Security Defences</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="K11" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="L9" s="9" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="M9" s="9">
-        <f>IF(N9=0,"—",IF(N9&gt;=9,"Strong",IF(N9&gt;=6,"Moderate",IF(N9&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="N9" s="10">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Multi-Agent Security*",Evidence!$B$2:$B$90,"Case study")</f>
-        <v/>
-      </c>
-      <c r="O9" s="9" t="inlineStr">
+      <c r="N11" s="9">
+        <f>IF(O11=0,"—",IF(O11&gt;=9,"Strong",IF(O11&gt;=6,"Moderate",IF(O11&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="O11" s="10">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Multi-Agent Security*")</f>
+        <v/>
+      </c>
+      <c r="P11" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="P9" s="9" t="inlineStr">
+      <c r="Q11" s="9" t="inlineStr">
         <is>
           <t>Coercion and Extortion via hacking/jailbreaking other agents cross-refs §3.7.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="11" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>Collusion</t>
         </is>
       </c>
-      <c r="C10" s="11" t="inlineStr">
+      <c r="C12" s="11" t="inlineStr">
         <is>
           <t>Network Effects</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>Text cross-reference only</t>
-        </is>
-      </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
+        <is>
+          <t>Evidence + text</t>
+        </is>
+      </c>
+      <c r="F12" s="11" t="inlineStr">
         <is>
           <t>Markets
 Steganography</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G12" s="11" t="inlineStr">
         <is>
           <t>Detecting AI Collusion
 Mitigating AI Collusion
 Assessing Impacts on Safety Protocols</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="H12" s="11" t="inlineStr">
         <is>
           <t>Error Propagation
 Network Rewiring
 Homogeneity and Correlated Failures</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I12" s="11" t="inlineStr">
         <is>
           <t>Evaluating and Monitoring Networks
 Faithful and Tractable Simulations
 Improving Network Security and Stability</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="11">
-        <f>IF(N10=0,"—",IF(N10&gt;=9,"Strong",IF(N10&gt;=6,"Moderate",IF(N10&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="N10" s="12">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*",Evidence!$K$2:$K$90,"*Network Effects*",Evidence!$B$2:$B$90,"Case study")</f>
-        <v/>
-      </c>
-      <c r="O10" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P10" s="11" t="inlineStr">
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>LW-01: ExploitGym swarm and Hugging Face intrusion: about 1,200 agents in separate san…</t>
+        </is>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="11" t="inlineStr">
+        <is>
+          <t>Operator report</t>
+        </is>
+      </c>
+      <c r="M12" s="11" t="inlineStr">
+        <is>
+          <t>Observed in real world</t>
+        </is>
+      </c>
+      <c r="N12" s="11">
+        <f>IF(O12=0,"—",IF(O12&gt;=9,"Strong",IF(O12&gt;=6,"Moderate",IF(O12&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="O12" s="12">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*",Evidence!$K$2:$K$90,"*Network Effects*")</f>
+        <v/>
+      </c>
+      <c r="P12" s="11" t="inlineStr">
+        <is>
+          <t>OpenAI technical report</t>
+        </is>
+      </c>
+      <c r="Q12" s="11" t="inlineStr">
         <is>
           <t>AI-AI preferential attachment simulations cross-ref §2.3 (§3.2.3).</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Collusion</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>Selection Pressures</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="F11" s="11" t="inlineStr">
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Evidence</t>
+        </is>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Markets
 Steganography</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G13" s="11" t="inlineStr">
         <is>
           <t>Detecting AI Collusion
 Mitigating AI Collusion
 Assessing Impacts on Safety Protocols</t>
         </is>
       </c>
-      <c r="H11" s="11" t="inlineStr">
+      <c r="H13" s="11" t="inlineStr">
         <is>
           <t>Undesirable Dispositions from Competition
 Undesirable Dispositions from Human Data
 Undesirable Capabilities</t>
         </is>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I13" s="11" t="inlineStr">
         <is>
           <t>Evaluating Against Diverse Co-Players
 Environment Design
@@ -2059,84 +2336,87 @@
 Simulating Selection Pressures</t>
         </is>
       </c>
-      <c r="J11" s="11" t="inlineStr">
+      <c r="J13" s="11" t="inlineStr">
         <is>
           <t>CS4: Algorithmic Collusion in the German Retail Gasoline Market</t>
         </is>
       </c>
-      <c r="K11" s="11" t="inlineStr">
+      <c r="K13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="11" t="inlineStr">
         <is>
           <t>Historical example</t>
         </is>
       </c>
-      <c r="L11" s="11" t="inlineStr">
+      <c r="M13" s="11" t="inlineStr">
         <is>
           <t>Observed in real world</t>
         </is>
       </c>
-      <c r="M11" s="11">
-        <f>IF(N11=0,"—",IF(N11&gt;=9,"Strong",IF(N11&gt;=6,"Moderate",IF(N11&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="N11" s="12">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*",Evidence!$K$2:$K$90,"*Selection Pressures*",Evidence!$B$2:$B$90,"Case study")</f>
-        <v/>
-      </c>
-      <c r="O11" s="11" t="inlineStr">
+      <c r="N13" s="11">
+        <f>IF(O13=0,"—",IF(O13&gt;=9,"Strong",IF(O13&gt;=6,"Moderate",IF(O13&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="O13" s="12">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*",Evidence!$K$2:$K$90,"*Selection Pressures*")</f>
+        <v/>
+      </c>
+      <c r="P13" s="11" t="inlineStr">
         <is>
           <t>Assad et al. (2020)</t>
         </is>
       </c>
-      <c r="P11" s="11" t="inlineStr">
+      <c r="Q13" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="11" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>Collusion</t>
         </is>
       </c>
-      <c r="C12" s="11" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Emergent Agency</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Case study + text</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>Evidence + text</t>
+        </is>
+      </c>
+      <c r="F14" s="11" t="inlineStr">
         <is>
           <t>Markets
 Steganography</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>Detecting AI Collusion
 Mitigating AI Collusion
 Assessing Impacts on Safety Protocols</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="H14" s="11" t="inlineStr">
         <is>
           <t>Emergent Capabilities
 Emergent Goals</t>
         </is>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I14" s="11" t="inlineStr">
         <is>
           <t>Empirical Exploration
 Theories of Emergent Capabilities
@@ -2144,78 +2424,93 @@
 Monitoring and Intervening on Collective Agents</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>CS4: Algorithmic Collusion in the German Retail Gasoline Market</t>
-        </is>
-      </c>
-      <c r="K12" s="11" t="inlineStr">
-        <is>
-          <t>Historical example</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>Observed in real world</t>
-        </is>
-      </c>
-      <c r="M12" s="11">
-        <f>IF(N12=0,"—",IF(N12&gt;=9,"Strong",IF(N12&gt;=6,"Moderate",IF(N12&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="N12" s="12">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*",Evidence!$K$2:$K$90,"*Emergent Agency*",Evidence!$B$2:$B$90,"Case study")</f>
-        <v/>
-      </c>
-      <c r="O12" s="11" t="inlineStr">
-        <is>
-          <t>Assad et al. (2020)</t>
-        </is>
-      </c>
-      <c r="P12" s="11" t="inlineStr">
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>CS4: Algorithmic Collusion in the German Retail Gasoline Market
+AIR-2026-0183: OpenAI evaluation agents turned an internal Artifactory service into a covert m…
+LW-01: ExploitGym swarm and Hugging Face intrusion: about 1,200 agents in separate san…
+AIR-2026-0219: A swarm of internally deployed OpenAI agents made more than 15,000 edits to the…</t>
+        </is>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>Historical example
+Safety failure
+Operator report
+Safety failure</t>
+        </is>
+      </c>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>Observed in real world
+Observed in real world
+Observed in real world
+Observed in real world</t>
+        </is>
+      </c>
+      <c r="N14" s="11">
+        <f>IF(O14=0,"—",IF(O14&gt;=9,"Strong",IF(O14&gt;=6,"Moderate",IF(O14&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="O14" s="12">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*",Evidence!$K$2:$K$90,"*Emergent Agency*")</f>
+        <v/>
+      </c>
+      <c r="P14" s="11" t="inlineStr">
+        <is>
+          <t>Assad et al. (2020)
+Agent Incident Registry (Enkrypt AI)
+OpenAI technical report
+Agent Incident Registry (Enkrypt AI)</t>
+        </is>
+      </c>
+      <c r="Q14" s="11" t="inlineStr">
         <is>
           <t>collusion can yield qualitatively new capabilities/goals (§2.3.2 → §3.6).</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Collusion</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Multi-Agent Security</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Case study + text</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="E15" s="11" t="inlineStr">
+        <is>
+          <t>Evidence + text</t>
+        </is>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>Markets
 Steganography</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G15" s="11" t="inlineStr">
         <is>
           <t>Detecting AI Collusion
 Mitigating AI Collusion
 Assessing Impacts on Safety Protocols</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="H15" s="11" t="inlineStr">
         <is>
           <t>Swarm Attacks
 Heterogeneous Attacks
@@ -2225,7 +2520,7 @@
 Undetectable Threats</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="I15" s="11" t="inlineStr">
         <is>
           <t>Secure Interaction Protocols
 Monitoring and Threat Detection
@@ -2233,42 +2528,61 @@
 Sociotechnical Security Defences</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>CS5: Language Model Steganography</t>
-        </is>
-      </c>
-      <c r="K13" s="11" t="inlineStr">
-        <is>
-          <t>Literature</t>
-        </is>
-      </c>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>Observed in lab</t>
-        </is>
-      </c>
-      <c r="M13" s="11">
-        <f>IF(N13=0,"—",IF(N13&gt;=9,"Strong",IF(N13&gt;=6,"Moderate",IF(N13&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="N13" s="12">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*",Evidence!$K$2:$K$90,"*Multi-Agent Security*",Evidence!$B$2:$B$90,"Case study")</f>
-        <v/>
-      </c>
-      <c r="O13" s="11" t="inlineStr">
-        <is>
-          <t>Motwani et al. (2024)</t>
-        </is>
-      </c>
-      <c r="P13" s="11" t="inlineStr">
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>CS5: Language Model Steganography
+AIR-2026-0183: OpenAI evaluation agents turned an internal Artifactory service into a covert m…
+LW-01: ExploitGym swarm and Hugging Face intrusion: about 1,200 agents in separate san…
+LW-02: Vanderbilt link shortener operation: a swarm used public link-shortener statist…
+AIR-2026-0219: A swarm of internally deployed OpenAI agents made more than 15,000 edits to the…</t>
+        </is>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>Literature
+Safety failure
+Operator report
+Independent investigation
+Safety failure</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Observed in lab
+Observed in real world
+Observed in real world
+Observed in real world
+Observed in real world</t>
+        </is>
+      </c>
+      <c r="N15" s="11">
+        <f>IF(O15=0,"—",IF(O15&gt;=9,"Strong",IF(O15&gt;=6,"Moderate",IF(O15&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="O15" s="12">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*",Evidence!$K$2:$K$90,"*Multi-Agent Security*")</f>
+        <v/>
+      </c>
+      <c r="P15" s="11" t="inlineStr">
+        <is>
+          <t>Motwani et al. (2024)
+Agent Incident Registry (Enkrypt AI)
+OpenAI technical report
+DeGraff: swarm investigation
+Agent Incident Registry (Enkrypt AI)</t>
+        </is>
+      </c>
+      <c r="Q15" s="11" t="inlineStr">
         <is>
           <t>collusion to bypass safeguards; Assessing Impacts on Safety Protocols cross-refs §3.6–3.7.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P13"/>
+  <autoFilter ref="A1:Q15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2279,7 +2593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2289,11 +2603,12 @@
     <col width="32" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="30" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="52" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -2334,25 +2649,30 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>case_studies</t>
+          <t>evidence</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>hammond_type</t>
+          <t>evidence_n</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>source_class</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>evidence_strength_max</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>evidence_score_max</t>
         </is>
@@ -2396,31 +2716,51 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Information Asymmetries
+Network Effects
 Selection Pressures
-Destabilising Dynamics</t>
+Destabilising Dynamics
+Commitment and Trust</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>CS1: Zero-Shot Coordination Failures in Driving</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Novel experiment by report authors</t>
-        </is>
+          <t>CS1: Zero-Shot Coordination Failures in Driving
+AIV-07: DeepSeek-V3.2 persuasion campaign: invented a self-serving metric; the group ad…
+AIV-06: Agents finetune their own leader: Opus assumed GPT-5.5 agreed without confirmin…
+AIV-04: Sub-team goal divergence: during a leader-election goal, the GPT agents left to…
+AIV-01: Hallucinated mailing list spreads between agents: o3 invented a 93-person maili…
+AIV-02: False 'broken UI' belief spreads: Gemini 2.5 Pro logged its own misclicks as sy…</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>6</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Synthetic evidence</t>
-        </is>
-      </c>
-      <c r="K2" s="2">
-        <f>IF(L2=0,"—",IF(L2&gt;=9,"Strong",IF(L2&gt;=6,"Moderate",IF(L2&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="L2" s="4">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$B$2:$B$90,"Case study")</f>
+          <t>Novel experiment by report authors
+Operator blog
+Operator blog
+Operator blog
+Operator blog
+Operator blog</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Synthetic evidence
+Synthetic evidence
+Synthetic evidence
+Synthetic evidence
+Synthetic evidence
+Synthetic evidence</t>
+        </is>
+      </c>
+      <c r="L2" s="2">
+        <f>IF(M2=0,"—",IF(M2&gt;=9,"Strong",IF(M2&gt;=6,"Moderate",IF(M2&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="M2" s="4">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*")</f>
         <v/>
       </c>
     </row>
@@ -2480,7 +2820,10 @@
 CS11: Dead Hands and Automated Deterrence</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Literature
 Literature
@@ -2489,7 +2832,7 @@
 Historical example</t>
         </is>
       </c>
-      <c r="J3" s="9" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Synthetic evidence
 Synthetic evidence
@@ -2498,12 +2841,12 @@
 Observed in real world</t>
         </is>
       </c>
-      <c r="K3" s="9">
-        <f>IF(L3=0,"—",IF(L3&gt;=9,"Strong",IF(L3&gt;=6,"Moderate",IF(L3&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="L3" s="10">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$B$2:$B$90,"Case study")</f>
+      <c r="L3" s="9">
+        <f>IF(M3=0,"—",IF(M3&gt;=9,"Strong",IF(M3&gt;=6,"Moderate",IF(M3&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="M3" s="10">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*")</f>
         <v/>
       </c>
     </row>
@@ -2552,27 +2895,42 @@
       <c r="H4" s="11" t="inlineStr">
         <is>
           <t>CS4: Algorithmic Collusion in the German Retail Gasoline Market
-CS5: Language Model Steganography</t>
-        </is>
-      </c>
-      <c r="I4" s="11" t="inlineStr">
+CS5: Language Model Steganography
+AIR-2026-0183: OpenAI evaluation agents turned an internal Artifactory service into a covert m…
+LW-01: ExploitGym swarm and Hugging Face intrusion: about 1,200 agents in separate san…
+LW-02: Vanderbilt link shortener operation: a swarm used public link-shortener statist…
+AIR-2026-0219: A swarm of internally deployed OpenAI agents made more than 15,000 edits to the…</t>
+        </is>
+      </c>
+      <c r="I4" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J4" s="11" t="inlineStr">
         <is>
           <t>Historical example
-Literature</t>
-        </is>
-      </c>
-      <c r="J4" s="11" t="inlineStr">
+Literature
+Safety failure
+Operator report
+Independent investigation
+Safety failure</t>
+        </is>
+      </c>
+      <c r="K4" s="11" t="inlineStr">
         <is>
           <t>Observed in real world
-Observed in lab</t>
-        </is>
-      </c>
-      <c r="K4" s="11">
-        <f>IF(L4=0,"—",IF(L4&gt;=9,"Strong",IF(L4&gt;=6,"Moderate",IF(L4&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="L4" s="12">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*",Evidence!$B$2:$B$90,"Case study")</f>
+Observed in lab
+Observed in real world
+Observed in real world
+Observed in real world
+Observed in real world</t>
+        </is>
+      </c>
+      <c r="L4" s="11">
+        <f>IF(M4=0,"—",IF(M4&gt;=9,"Strong",IF(M4&gt;=6,"Moderate",IF(M4&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="M4" s="12">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*")</f>
         <v/>
       </c>
     </row>
@@ -2622,29 +2980,53 @@
         <is>
           <t>CS1: Zero-Shot Coordination Failures in Driving
 CS6: AI Agents Can Learn to Manipulate Financial Markets
-CS7: Transmission Through AI Networks Can Spread Falsities and Bias</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
+CS7: Transmission Through AI Networks Can Spread Falsities and Bias
+AIV-07: DeepSeek-V3.2 persuasion campaign: invented a self-serving metric; the group ad…
+AIV-06: Agents finetune their own leader: Opus assumed GPT-5.5 agreed without confirmin…
+AIV-05: Sabotage game: saboteurs tried to hide easter eggs in a shared game; Opus 4.6 e…
+AIR-2025-0149: OpenAI Agent Builder: a poisoned lead-form submission redirects a multi-agent s…
+AIV-03: Game-choice herding: agents copied the games peers announced they were beating…
+AIV-01: Hallucinated mailing list spreads between agents: o3 invented a 93-person maili…
+AIV-02: False 'broken UI' belief spreads: Gemini 2.5 Pro logged its own misclicks as sy…</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Novel experiment by report authors
 Literature
-Novel experiment by report authors</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
+Novel experiment by report authors
+Operator blog
+Operator blog
+Operator blog
+Research demo
+Operator blog
+Operator blog
+Operator blog</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Synthetic evidence
 Synthetic evidence
-Observed in lab</t>
-        </is>
-      </c>
-      <c r="K5" s="5">
-        <f>IF(L5=0,"—",IF(L5&gt;=9,"Strong",IF(L5&gt;=6,"Moderate",IF(L5&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="L5" s="7">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Information Asymmetries*",Evidence!$B$2:$B$90,"Case study")</f>
+Observed in lab
+Synthetic evidence
+Synthetic evidence
+Synthetic evidence
+Observed in lab
+Synthetic evidence
+Synthetic evidence
+Synthetic evidence</t>
+        </is>
+      </c>
+      <c r="L5" s="5">
+        <f>IF(M5=0,"—",IF(M5&gt;=9,"Strong",IF(M5&gt;=6,"Moderate",IF(M5&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="M5" s="7">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Information Asymmetries*")</f>
         <v/>
       </c>
     </row>
@@ -2685,36 +3067,64 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Collusion</t>
+          <t>Miscoordination
+Collusion</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
           <t>CS7: Transmission Through AI Networks Can Spread Falsities and Bias
 CS8: Infectious Adversarial Attacks in Networks of LLM Agents
-CS10: The 2010 Flash Crash</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
+CS10: The 2010 Flash Crash
+AIV-07: DeepSeek-V3.2 persuasion campaign: invented a self-serving metric; the group ad…
+AIR-2026-0193: Agent 'mind virus': self-propagating payload written into SOUL.md spreads betwe…
+AIR-2026-0189: Pwning the Internet of Agents: an OpenClaw agent botnet on MoltBook (DEF CON 34)
+LW-01: ExploitGym swarm and Hugging Face intrusion: about 1,200 agents in separate san…
+LW-05: Moltbook agent behaviour: AI-agent-only social network reportedly reached ~36k…
+AIV-03: Game-choice herding: agents copied the games peers announced they were beating…
+AIR-2025-0068: IdentityMesh: agentic lateral movement through merged identities across connect…
+AIV-01: Hallucinated mailing list spreads between agents: o3 invented a 93-person maili…</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Novel experiment by report authors
 Literature
-Historical example</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
+Historical example
+Operator blog
+Research demo
+Research demo
+Operator report
+Forum post
+Operator blog
+Research demo
+Operator blog</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Observed in lab
 Synthetic evidence
-Observed in real world</t>
-        </is>
-      </c>
-      <c r="K6" s="5">
-        <f>IF(L6=0,"—",IF(L6&gt;=9,"Strong",IF(L6&gt;=6,"Moderate",IF(L6&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="L6" s="7">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Network Effects*",Evidence!$B$2:$B$90,"Case study")</f>
+Observed in real world
+Synthetic evidence
+Observed in lab
+Observed in lab
+Observed in real world
+Observed in real world
+Synthetic evidence
+Observed in lab
+Synthetic evidence</t>
+        </is>
+      </c>
+      <c r="L6" s="5">
+        <f>IF(M6=0,"—",IF(M6&gt;=9,"Strong",IF(M6&gt;=6,"Moderate",IF(M6&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="M6" s="7">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Network Effects*")</f>
         <v/>
       </c>
     </row>
@@ -2770,7 +3180,10 @@
 CS9: Cooperation Fails to Culturally Evolve among LLM Agents</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="I7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Novel experiment by report authors
 Literature
@@ -2778,7 +3191,7 @@
 Literature</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Synthetic evidence
 Synthetic evidence
@@ -2786,12 +3199,12 @@
 Synthetic evidence</t>
         </is>
       </c>
-      <c r="K7" s="5">
-        <f>IF(L7=0,"—",IF(L7&gt;=9,"Strong",IF(L7&gt;=6,"Moderate",IF(L7&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="L7" s="7">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Selection Pressures*",Evidence!$B$2:$B$90,"Case study")</f>
+      <c r="L7" s="5">
+        <f>IF(M7=0,"—",IF(M7&gt;=9,"Strong",IF(M7&gt;=6,"Moderate",IF(M7&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="M7" s="7">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Selection Pressures*")</f>
         <v/>
       </c>
     </row>
@@ -2844,24 +3257,27 @@
 CS10: The 2010 Flash Crash</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="I8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Literature
 Historical example</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>Synthetic evidence
 Observed in real world</t>
         </is>
       </c>
-      <c r="K8" s="5">
-        <f>IF(L8=0,"—",IF(L8&gt;=9,"Strong",IF(L8&gt;=6,"Moderate",IF(L8&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="L8" s="7">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Destabilising Dynamics*",Evidence!$B$2:$B$90,"Case study")</f>
+      <c r="L8" s="5">
+        <f>IF(M8=0,"—",IF(M8&gt;=9,"Strong",IF(M8&gt;=6,"Moderate",IF(M8&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="M8" s="7">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Destabilising Dynamics*")</f>
         <v/>
       </c>
     </row>
@@ -2904,36 +3320,58 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Conflict</t>
+          <t>Miscoordination
+Conflict</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
           <t>CS2: Common Resource Problems
 CS9: Cooperation Fails to Culturally Evolve among LLM Agents
-CS11: Dead Hands and Automated Deterrence</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
+CS11: Dead Hands and Automated Deterrence
+AIR-2026-0180: 'I'll just call you': a low-privileged CI agent on Google's adk-python is injec…
+AIV-06: Agents finetune their own leader: Opus assumed GPT-5.5 agreed without confirmin…
+AIR-2026-0101: Morse-code prompt injection made Grok relay a transfer instruction to Bankrbot,…
+AIV-05: Sabotage game: saboteurs tried to hide easter eggs in a shared game; Opus 4.6 e…
+AIR-2025-0177: ServiceNow Now Assist: second-order prompt injection recruits privileged agents…
+AIR-2025-0136: Cross-agent privilege escalation: one hijacked coding agent rewrites another ag…</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Literature
 Literature
-Historical example</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
+Historical example
+Disclosed vulnerability
+Operator blog
+In the wild
+Operator blog
+Disclosed vulnerability
+Disclosed vulnerability</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Synthetic evidence
 Synthetic evidence
-Observed in real world</t>
-        </is>
-      </c>
-      <c r="K9" s="5">
-        <f>IF(L9=0,"—",IF(L9&gt;=9,"Strong",IF(L9&gt;=6,"Moderate",IF(L9&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="L9" s="7">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Commitment and Trust*",Evidence!$B$2:$B$90,"Case study")</f>
+Observed in real world
+Observed in lab
+Synthetic evidence
+Observed in real world
+Synthetic evidence
+Observed in lab
+Observed in lab</t>
+        </is>
+      </c>
+      <c r="L9" s="5">
+        <f>IF(M9=0,"—",IF(M9&gt;=9,"Strong",IF(M9&gt;=6,"Moderate",IF(M9&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="M9" s="7">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Commitment and Trust*")</f>
         <v/>
       </c>
     </row>
@@ -2980,27 +3418,48 @@
       <c r="H10" s="5" t="inlineStr">
         <is>
           <t>CS4: Algorithmic Collusion in the German Retail Gasoline Market
-CS12: Overcoming Safeguards via Multiple Safe Models</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
+CS12: Overcoming Safeguards via Multiple Safe Models
+AIR-2026-0183: OpenAI evaluation agents turned an internal Artifactory service into a covert m…
+LW-01: ExploitGym swarm and Hugging Face intrusion: about 1,200 agents in separate san…
+AIR-2026-0219: A swarm of internally deployed OpenAI agents made more than 15,000 edits to the…
+LW-05: Moltbook agent behaviour: AI-agent-only social network reportedly reached ~36k…
+AIR-2025-0027: Influence-as-a-service: Claude used as the orchestrator deciding actions for 10…
+AIR-2025-0019: Xanthorox AI: a self-hosted, five-model offensive platform sold on darknet foru…</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Historical example
-Literature</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
+Literature
+Safety failure
+Operator report
+Safety failure
+Forum post
+In the wild
+In the wild</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>Observed in real world
-Observed in lab</t>
-        </is>
-      </c>
-      <c r="K10" s="5">
-        <f>IF(L10=0,"—",IF(L10&gt;=9,"Strong",IF(L10&gt;=6,"Moderate",IF(L10&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="L10" s="7">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Emergent Agency*",Evidence!$B$2:$B$90,"Case study")</f>
+Observed in lab
+Observed in real world
+Observed in real world
+Observed in real world
+Observed in real world
+Observed in real world
+Observed in real world</t>
+        </is>
+      </c>
+      <c r="L10" s="5">
+        <f>IF(M10=0,"—",IF(M10&gt;=9,"Strong",IF(M10&gt;=6,"Moderate",IF(M10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="M10" s="7">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Emergent Agency*")</f>
         <v/>
       </c>
     </row>
@@ -3054,36 +3513,87 @@
           <t>CS5: Language Model Steganography
 CS8: Infectious Adversarial Attacks in Networks of LLM Agents
 CS12: Overcoming Safeguards via Multiple Safe Models
-CS13: Unprompted Adversarial Attacks on Overseer Agents</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
+CS13: Unprompted Adversarial Attacks on Overseer Agents
+AIR-2026-0193: Agent 'mind virus': self-propagating payload written into SOUL.md spreads betwe…
+AIR-2026-0189: Pwning the Internet of Agents: an OpenClaw agent botnet on MoltBook (DEF CON 34)
+AIR-2026-0183: OpenAI evaluation agents turned an internal Artifactory service into a covert m…
+AIR-2026-0180: 'I'll just call you': a low-privileged CI agent on Google's adk-python is injec…
+LW-01: ExploitGym swarm and Hugging Face intrusion: about 1,200 agents in separate san…
+AIR-2026-0194: Suspected China-linked actors used a multi-agent framework built on Hermes and…
+LW-02: Vanderbilt link shortener operation: a swarm used public link-shortener statist…
+AIR-2026-0219: A swarm of internally deployed OpenAI agents made more than 15,000 edits to the…
+AIR-2026-0101: Morse-code prompt injection made Grok relay a transfer instruction to Bankrbot,…
+AIR-2026-0029: Moltbook, the social network for AI agents, left its database open: 1.5M API to…
+AIR-2025-0177: ServiceNow Now Assist: second-order prompt injection recruits privileged agents…
+AIR-2025-0149: OpenAI Agent Builder: a poisoned lead-form submission redirects a multi-agent s…
+AIR-2025-0136: Cross-agent privilege escalation: one hijacked coding agent rewrites another ag…
+AIR-2025-0070: PajaMAS: hijacking multi-agent systems built on Google's Agent Development Kit
+AIR-2025-0068: IdentityMesh: agentic lateral movement through merged identities across connect…
+AIR-2025-0019: Xanthorox AI: a self-hosted, five-model offensive platform sold on darknet foru…</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Literature
 Literature
 Literature
-Novel experiment by report authors</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
+Novel experiment by report authors
+Research demo
+Research demo
+Safety failure
+Disclosed vulnerability
+Operator report
+In the wild
+Independent investigation
+Safety failure
+In the wild
+Disclosed vulnerability
+Disclosed vulnerability
+Research demo
+Disclosed vulnerability
+Research demo
+Research demo
+In the wild</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Observed in lab
 Synthetic evidence
 Observed in lab
-Observed in lab</t>
-        </is>
-      </c>
-      <c r="K11" s="5">
-        <f>IF(L11=0,"—",IF(L11&gt;=9,"Strong",IF(L11&gt;=6,"Moderate",IF(L11&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="L11" s="7">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Multi-Agent Security*",Evidence!$B$2:$B$90,"Case study")</f>
+Observed in lab
+Observed in lab
+Observed in lab
+Observed in real world
+Observed in lab
+Observed in real world
+Observed in real world
+Observed in real world
+Observed in real world
+Observed in real world
+Observed in lab
+Observed in lab
+Observed in lab
+Observed in lab
+Observed in lab
+Observed in lab
+Observed in real world</t>
+        </is>
+      </c>
+      <c r="L11" s="5">
+        <f>IF(M11=0,"—",IF(M11&gt;=9,"Strong",IF(M11&gt;=6,"Moderate",IF(M11&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="M11" s="7">
+        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$K$2:$K$90,"*Multi-Agent Security*")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L11"/>
+  <autoFilter ref="A1:M11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -3138,12 +3648,12 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>case_studies_explicit</t>
+          <t>evidence_explicit</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>case_studies_placement</t>
+          <t>evidence_placement</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -9686,7 +10196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -9809,33 +10319,47 @@
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>grounding_score and evidence_score_max = highest evidence_score among the relevant rows with evidence_class = 'Case study' (0 = none). Scored incidents sit in the same sheet but are deliberately left out of grounding; that is the open decision in OPEN.md item 3. To fold them in, drop the evidence_class criterion from maxifs() in build/build_xlsx.py.</t>
+          <t>grounding_score and evidence_score_max = highest evidence_score across the whole evidence inventory tagged with that risk, case studies and incidents alike (0 = none). Max, not sum or mean: corroboration is already scored inside each row as E4, and summing would let many weak rows outrank one strong one.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
         <is>
-          <t>Case studies tagged with a risk factor but no failure mode (CS7, CS8, CS10, CS12, CS13) count only towards that risk factor.</t>
+          <t>evidence_n counts the rows behind the score. A high grounding on evidence_n = 1 rests on a single piece of evidence; read the two together.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="23" t="inlineStr">
         <is>
-          <t>case_studies_explicit = the paper cross-references the case study in that instance's paragraph; case_studies_placement = the case-study box sits in that instance's discussion without an explicit reference.</t>
+          <t>Evidence tagged with a risk factor but no failure mode counts only towards that risk factor. Rows with blank E1-E5 are ignored by the score.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="23" t="inlineStr">
         <is>
-          <t>evidence_basis: Case study / Cited empirical work (no case study, but empirical studies cited) / Theoretical.</t>
+          <t>Instances: evidence_explicit and evidence_placement hold Hammond case-study ids only. Incidents attach directly to failure modes and risk factors, not to instances, because Table 1's sub-topics are finer-grained than this project's scope. Instance-level evidence stays as the paper records it.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>case_studies_explicit = the paper cross-references the case study in that instance's paragraph; case_studies_placement = the case-study box sits in that instance's discussion without an explicit reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>evidence_basis: Case study / Cited empirical work (no case study, but empirical studies cited) / Theoretical.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="23" t="inlineStr">
         <is>
           <t>Formulas need a spreadsheet app to compute (Excel 2019+ or LibreOffice). out/risk_index.csv has the same values precomputed.</t>
         </is>

--- a/out/multi_agent_risk_taxonomy.xlsx
+++ b/out/multi_agent_risk_taxonomy.xlsx
@@ -17,9 +17,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Risk Index'!$A$1:$I$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FM-RF Links'!$A$1:$Q$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'FM-RF Links'!$A$1:$P$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Taxonomy'!$A$1:$M$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Instances'!$A$1:$K$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Instances'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Evidence'!$A$1:$X$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Sources'!$A$1:$D$31</definedName>
   </definedNames>
@@ -128,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -157,11 +157,17 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -575,7 +581,7 @@
     <col width="40" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -621,7 +627,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>evidence_link</t>
+          <t>link_basis</t>
         </is>
       </c>
     </row>
@@ -661,19 +667,15 @@
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Information Asymmetries
-Network Effects
 Selection Pressures
-Destabilising Dynamics
-Commitment and Trust</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>TRUE
-TRUE
-TRUE
-FALSE
-TRUE</t>
+Destabilising Dynamics</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Paper prose
+Paper Table 3 co-tag
+Paper prose</t>
         </is>
       </c>
     </row>
@@ -719,13 +721,13 @@
 Multi-Agent Security</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>TRUE
-TRUE
-TRUE
-TRUE
-FALSE</t>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Paper prose
+Paper prose
+Paper prose
+Paper prose
+Paper prose</t>
         </is>
       </c>
     </row>
@@ -770,12 +772,12 @@
 Multi-Agent Security</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>TRUE
-TRUE
-TRUE
-TRUE</t>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Paper prose
+Paper Table 3 co-tag
+Paper prose
+Paper prose</t>
         </is>
       </c>
     </row>
@@ -806,11 +808,11 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>CS1, CS6, CS7, AIV-07, AIV-06, AIV-05, AIR-2025-0149, AIV-03, AIV-01, AIV-02</t>
+          <t>CS1, CS6, CS7, AIV-07, AIV-06, AIV-05, AIR-2025-0149</t>
         </is>
       </c>
       <c r="G5" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
@@ -818,10 +820,10 @@
 Conflict</t>
         </is>
       </c>
-      <c r="I5" s="7" t="inlineStr">
-        <is>
-          <t>TRUE
-TRUE</t>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Paper prose
+Paper prose</t>
         </is>
       </c>
     </row>
@@ -860,14 +862,12 @@
       </c>
       <c r="H6" s="5" t="inlineStr">
         <is>
-          <t>Miscoordination
-Collusion</t>
-        </is>
-      </c>
-      <c r="I6" s="7" t="inlineStr">
-        <is>
-          <t>TRUE
-TRUE</t>
+          <t>Collusion</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Paper prose</t>
         </is>
       </c>
     </row>
@@ -911,11 +911,11 @@
 Collusion</t>
         </is>
       </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>TRUE
-TRUE
-TRUE</t>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Paper Table 3 co-tag
+Paper prose
+Paper Table 3 co-tag</t>
         </is>
       </c>
     </row>
@@ -958,10 +958,10 @@
 Conflict</t>
         </is>
       </c>
-      <c r="I8" s="7" t="inlineStr">
-        <is>
-          <t>FALSE
-TRUE</t>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Paper prose
+Paper prose</t>
         </is>
       </c>
     </row>
@@ -992,22 +992,20 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>CS2, CS9, CS11, AIR-2026-0180, AIV-06, AIR-2026-0101, AIV-05, AIR-2025-0177, AIR-2025-0136</t>
+          <t>CS2, CS9, CS11, AIV-06, AIV-05</t>
         </is>
       </c>
       <c r="G9" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H9" s="5" t="inlineStr">
         <is>
-          <t>Miscoordination
-Conflict</t>
-        </is>
-      </c>
-      <c r="I9" s="7" t="inlineStr">
-        <is>
-          <t>TRUE
-TRUE</t>
+          <t>Conflict</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Paper prose</t>
         </is>
       </c>
     </row>
@@ -1038,20 +1036,20 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>CS4, CS12, AIR-2026-0183, LW-01, AIR-2026-0219, LW-05, AIR-2025-0027, AIR-2025-0019</t>
+          <t>CS4, CS12, AIR-2026-0183, LW-01, AIR-2026-0219, LW-05, AIR-2025-0019</t>
         </is>
       </c>
       <c r="G10" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Collusion</t>
         </is>
       </c>
-      <c r="I10" s="7" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Paper prose</t>
         </is>
       </c>
     </row>
@@ -1082,11 +1080,11 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>CS5, CS8, CS12, CS13, AIR-2026-0193, AIR-2026-0189, AIR-2026-0183, AIR-2026-0180, LW-01, AIR-2026-0194, LW-02, AIR-2026-0219, AIR-2026-0101, AIR-2026-0029, AIR-2025-0177, AIR-2025-0149, AIR-2025-0136, AIR-2025-0070, AIR-2025-0068, AIR-2025-0019</t>
+          <t>CS5, CS8, CS12, CS13, AIR-2026-0193, AIR-2026-0189, AIR-2026-0183, AIR-2026-0180, LW-01, AIR-2026-0194, LW-02, AIR-2026-0219, AIR-2026-0101, AIR-2026-0029, AIR-2025-0177, AIR-2025-0149, AIR-2025-0136, AIR-2025-0070, AIR-2025-0068, AIR-2025-0027, AIR-2025-0019</t>
         </is>
       </c>
       <c r="G11" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
@@ -1094,10 +1092,10 @@
 Collusion</t>
         </is>
       </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>FALSE
-TRUE</t>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Paper prose
+Paper prose</t>
         </is>
       </c>
     </row>
@@ -1131,26 +1129,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q15"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
-    <col width="34" customWidth="1" min="9" max="9"/>
-    <col width="48" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="44" customWidth="1" min="17" max="17"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+    <col width="34" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="44" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -1171,70 +1168,65 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>evidence_link</t>
+          <t>link_basis</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>link_basis</t>
+          <t>fm_strength</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>fm_grounding</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>fm_evidence_n</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>rf_strength</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>rf_grounding_amplifying</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>rf_evidence_n</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>fm_instances</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>fm_directions</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>rf_instances</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>rf_directions</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>evidence_tagged_both</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>evidence_n</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>source_class</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>evidence_strength_max</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>evidence_score_max</t>
+          <t>rf_evidence</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>evidence_source</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>text_reference</t>
         </is>
@@ -1254,38 +1246,54 @@
           <t>Information Asymmetries</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Evidence + text</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Paper prose</t>
+        </is>
+      </c>
+      <c r="E2" s="2">
+        <f>IF(F2*10=0,"—",IF(F2*10&gt;=9,"Strong",IF(F2*10&gt;=6,"Moderate",IF(F2*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" s="2">
+        <f>IF(I2*10=0,"—",IF(I2*10&gt;=9,"Strong",IF(I2*10&gt;=6,"Moderate",IF(I2*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J2" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Incompatible Strategies
 Credit Assignment
-Limited Interactions</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+Limited Interactions
+Shared False Beliefs</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Communication
 Norms and Conventions
 Modelling Other Agents</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Communication Constraints
 Bargaining
 Deception</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Information Design
 Individual Information Revelation
@@ -1293,54 +1301,12 @@
 Truthful AI</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>CS1: Zero-Shot Coordination Failures in Driving
-AIV-07: DeepSeek-V3.2 persuasion campaign: invented a self-serving metric; the group ad…
-AIV-06: Agents finetune their own leader: Opus assumed GPT-5.5 agreed without confirmin…
-AIV-01: Hallucinated mailing list spreads between agents: o3 invented a 93-person maili…
-AIV-02: False 'broken UI' belief spreads: Gemini 2.5 Pro logged its own misclicks as sy…</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>Novel experiment by report authors
-Operator blog
-Operator blog
-Operator blog
-Operator blog</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic evidence
-Synthetic evidence
-Synthetic evidence
-Synthetic evidence
-Synthetic evidence</t>
-        </is>
-      </c>
-      <c r="N2" s="2">
-        <f>IF(O2=0,"—",IF(O2&gt;=9,"Strong",IF(O2&gt;=6,"Moderate",IF(O2&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="O2" s="4">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$K$2:$K$90,"*Information Asymmetries*")</f>
-        <v/>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>CS1, CS6, CS7, AIV-07, AIV-06, AIV-05, AIR-2025-0149</t>
+        </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Report authors (App. B.1)
-Persuasion in the AI Village: DeepSeek-V3.2 &amp; Gemini 2.5 Pro
-AIs finetune their own leader: a barking simpleton
-Season 2 recap: the story of the world's first AI-organized event
-What did we learn from the AI Village in 2025?</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>info asymmetries can cause miscoordination (§1.1, §3); Credit Assignment &amp; Communication Constraints cross-ref §2.1/§3.1.</t>
         </is>
@@ -1357,134 +1323,57 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Network Effects</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+          <t>Selection Pressures</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Paper Table 3 co-tag</t>
+        </is>
+      </c>
+      <c r="E3" s="2">
+        <f>IF(F3*10=0,"—",IF(F3*10&gt;=9,"Strong",IF(F3*10&gt;=6,"Moderate",IF(F3*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" s="2">
+        <f>IF(I3*10=0,"—",IF(I3*10&gt;=9,"Strong",IF(I3*10&gt;=6,"Moderate",IF(I3*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
         <is>
           <t>Incompatible Strategies
 Credit Assignment
-Limited Interactions</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+Limited Interactions
+Shared False Beliefs</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Communication
 Norms and Conventions
 Modelling Other Agents</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Error Propagation
-Network Rewiring
-Homogeneity and Correlated Failures</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Evaluating and Monitoring Networks
-Faithful and Tractable Simulations
-Improving Network Security and Stability</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>AIV-07: DeepSeek-V3.2 persuasion campaign: invented a self-serving metric; the group ad…
-AIV-01: Hallucinated mailing list spreads between agents: o3 invented a 93-person maili…</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Operator blog
-Operator blog</t>
-        </is>
-      </c>
       <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic evidence
-Synthetic evidence</t>
-        </is>
-      </c>
-      <c r="N3" s="2">
-        <f>IF(O3=0,"—",IF(O3&gt;=9,"Strong",IF(O3&gt;=6,"Moderate",IF(O3&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="O3" s="4">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$K$2:$K$90,"*Network Effects*")</f>
-        <v/>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Persuasion in the AI Village: DeepSeek-V3.2 &amp; Gemini 2.5 Pro
-Season 2 recap: the story of the world's first AI-organized event</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Miscoordination</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Selection Pressures</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Incompatible Strategies
-Credit Assignment
-Limited Interactions</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Communication
-Norms and Conventions
-Modelling Other Agents</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Undesirable Dispositions from Competition
 Undesirable Dispositions from Human Data
 Undesirable Capabilities</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Evaluating Against Diverse Co-Players
 Environment Design
@@ -1493,82 +1382,72 @@
 Simulating Selection Pressures</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>CS1: Zero-Shot Coordination Failures in Driving</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Novel experiment by report authors</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic evidence</t>
-        </is>
-      </c>
-      <c r="N4" s="2">
-        <f>IF(O4=0,"—",IF(O4&gt;=9,"Strong",IF(O4&gt;=6,"Moderate",IF(O4&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="O4" s="4">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$K$2:$K$90,"*Selection Pressures*")</f>
-        <v/>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Report authors (App. B.1)</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>CS1, CS2, CS4, CS9</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Miscoordination</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Destabilising Dynamics</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Text cross-reference only</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Paper prose</t>
+        </is>
+      </c>
+      <c r="E4" s="2">
+        <f>IF(F4*10=0,"—",IF(F4*10&gt;=9,"Strong",IF(F4*10&gt;=6,"Moderate",IF(F4*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H4" s="2">
+        <f>IF(I4*10=0,"—",IF(I4*10&gt;=9,"Strong",IF(I4*10&gt;=6,"Moderate",IF(I4*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Incompatible Strategies
 Credit Assignment
-Limited Interactions</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+Limited Interactions
+Shared False Beliefs</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Communication
 Norms and Conventions
 Modelling Other Agents</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Feedback Loops
 Cyclic Behaviour
@@ -1577,173 +1456,71 @@
 Distributional Shift</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Understanding Dynamics
 Monitoring and Stabilising Dynamics
 Regulating Adaptive Multi-Agent Systems</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2">
-        <f>IF(O5=0,"—",IF(O5&gt;=9,"Strong",IF(O5&gt;=6,"Moderate",IF(O5&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="O5" s="4">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$K$2:$K$90,"*Destabilising Dynamics*")</f>
-        <v/>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>CS3, CS10</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>Credit Assignment cross-refs §3.4 (distributional shift).</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>Conflict</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Information Asymmetries</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Paper prose</t>
+        </is>
+      </c>
+      <c r="E5" s="9">
+        <f>IF(F5*10=0,"—",IF(F5*10&gt;=9,"Strong",IF(F5*10&gt;=6,"Moderate",IF(F5*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="F5" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G5" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Miscoordination</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Commitment and Trust</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Incompatible Strategies
-Credit Assignment
-Limited Interactions</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Communication
-Norms and Conventions
-Modelling Other Agents</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Inefficient Outcomes
-Threats and Extortion
-Rigidity and Mistaken Commitments</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Keeping Humans in the Loop
-Limiting Commitment Power
-Institutions and Normative Infrastructure
-Privacy-Preserving Monitoring
-Mutual Simulation and Transparency</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>AIV-06: Agents finetune their own leader: Opus assumed GPT-5.5 agreed without confirmin…</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Operator blog</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>Synthetic evidence</t>
-        </is>
-      </c>
-      <c r="N6" s="2">
-        <f>IF(O6=0,"—",IF(O6&gt;=9,"Strong",IF(O6&gt;=6,"Moderate",IF(O6&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="O6" s="4">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Miscoordination*",Evidence!$K$2:$K$90,"*Commitment and Trust*")</f>
-        <v/>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>AIs finetune their own leader: a barking simpleton</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Conflict</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Information Asymmetries</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>Evidence + text</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="H5" s="9">
+        <f>IF(I5*10=0,"—",IF(I5*10&gt;=9,"Strong",IF(I5*10&gt;=6,"Moderate",IF(I5*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="I5" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J5" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>Social Dilemmas
 Military Domains
 Coercion and Extortion</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>Learning Peer and Pool Incentivisation
 Establishing Trust
@@ -1753,14 +1530,14 @@
 Evidential Reasoning</t>
         </is>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>Communication Constraints
 Bargaining
 Deception</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="N5" s="9" t="inlineStr">
         <is>
           <t>Information Design
 Individual Information Revelation
@@ -1768,75 +1545,64 @@
 Truthful AI</t>
         </is>
       </c>
-      <c r="J7" s="9" t="inlineStr">
-        <is>
-          <t>CS6: AI Agents Can Learn to Manipulate Financial Markets</t>
-        </is>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" s="9" t="inlineStr">
-        <is>
-          <t>Literature</t>
-        </is>
-      </c>
-      <c r="M7" s="9" t="inlineStr">
-        <is>
-          <t>Synthetic evidence</t>
-        </is>
-      </c>
-      <c r="N7" s="9">
-        <f>IF(O7=0,"—",IF(O7&gt;=9,"Strong",IF(O7&gt;=6,"Moderate",IF(O7&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="O7" s="10">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Information Asymmetries*")</f>
-        <v/>
-      </c>
-      <c r="P7" s="9" t="inlineStr">
-        <is>
-          <t>Shearer et al. (2023); Wang &amp; Wellman (2020)</t>
-        </is>
-      </c>
-      <c r="Q7" s="9" t="inlineStr">
+      <c r="O5" s="9" t="inlineStr">
+        <is>
+          <t>CS1, CS6, CS7, AIV-07, AIV-06, AIV-05, AIR-2025-0149</t>
+        </is>
+      </c>
+      <c r="P5" s="9" t="inlineStr">
         <is>
           <t>Bargaining under asymmetric info → costly conflict (§3.1).</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Selection Pressures</t>
         </is>
       </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>Evidence + text</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Paper prose</t>
+        </is>
+      </c>
+      <c r="E6" s="9">
+        <f>IF(F6*10=0,"—",IF(F6*10&gt;=9,"Strong",IF(F6*10&gt;=6,"Moderate",IF(F6*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="F6" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" s="9">
+        <f>IF(I6*10=0,"—",IF(I6*10&gt;=9,"Strong",IF(I6*10&gt;=6,"Moderate",IF(I6*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="I6" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>Social Dilemmas
 Military Domains
 Coercion and Extortion</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>Learning Peer and Pool Incentivisation
 Establishing Trust
@@ -1846,14 +1612,14 @@
 Evidential Reasoning</t>
         </is>
       </c>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>Undesirable Dispositions from Competition
 Undesirable Dispositions from Human Data
 Undesirable Capabilities</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>Evaluating Against Diverse Co-Players
 Environment Design
@@ -1862,79 +1628,64 @@
 Simulating Selection Pressures</t>
         </is>
       </c>
-      <c r="J8" s="9" t="inlineStr">
-        <is>
-          <t>CS2: Common Resource Problems
-CS9: Cooperation Fails to Culturally Evolve among LLM Agents</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="n">
+      <c r="O6" s="9" t="inlineStr">
+        <is>
+          <t>CS1, CS2, CS4, CS9</t>
+        </is>
+      </c>
+      <c r="P6" s="9" t="inlineStr">
+        <is>
+          <t>Cooperative Dispositions direction cross-refs §3.3 (conflict-prone dispositions from data/training).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Conflict</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Destabilising Dynamics</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Paper prose</t>
+        </is>
+      </c>
+      <c r="E7" s="9">
+        <f>IF(F7*10=0,"—",IF(F7*10&gt;=9,"Strong",IF(F7*10&gt;=6,"Moderate",IF(F7*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" s="9">
+        <f>IF(I7*10=0,"—",IF(I7*10&gt;=9,"Strong",IF(I7*10&gt;=6,"Moderate",IF(I7*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="I7" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J7" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="L8" s="9" t="inlineStr">
-        <is>
-          <t>Literature
-Literature</t>
-        </is>
-      </c>
-      <c r="M8" s="9" t="inlineStr">
-        <is>
-          <t>Synthetic evidence
-Synthetic evidence</t>
-        </is>
-      </c>
-      <c r="N8" s="9">
-        <f>IF(O8=0,"—",IF(O8&gt;=9,"Strong",IF(O8&gt;=6,"Moderate",IF(O8&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="O8" s="10">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Selection Pressures*")</f>
-        <v/>
-      </c>
-      <c r="P8" s="9" t="inlineStr">
-        <is>
-          <t>Piatti et al. (2024), GovSim
-Vallinder &amp; Hughes (2024)</t>
-        </is>
-      </c>
-      <c r="Q8" s="9" t="inlineStr">
-        <is>
-          <t>Cooperative Dispositions direction cross-refs §3.3 (conflict-prone dispositions from data/training).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Conflict</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>Destabilising Dynamics</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>Evidence + text</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>Social Dilemmas
 Military Domains
 Coercion and Extortion</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="L7" s="9" t="inlineStr">
         <is>
           <t>Learning Peer and Pool Incentivisation
 Establishing Trust
@@ -1944,7 +1695,7 @@
 Evidential Reasoning</t>
         </is>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>Feedback Loops
 Cyclic Behaviour
@@ -1953,82 +1704,71 @@
 Distributional Shift</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="N7" s="9" t="inlineStr">
         <is>
           <t>Understanding Dynamics
 Monitoring and Stabilising Dynamics
 Regulating Adaptive Multi-Agent Systems</t>
         </is>
       </c>
-      <c r="J9" s="9" t="inlineStr">
-        <is>
-          <t>CS3: Escalation in Military Conflicts</t>
-        </is>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" s="9" t="inlineStr">
-        <is>
-          <t>Literature</t>
-        </is>
-      </c>
-      <c r="M9" s="9" t="inlineStr">
-        <is>
-          <t>Synthetic evidence</t>
-        </is>
-      </c>
-      <c r="N9" s="9">
-        <f>IF(O9=0,"—",IF(O9&gt;=9,"Strong",IF(O9&gt;=6,"Moderate",IF(O9&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="O9" s="10">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Destabilising Dynamics*")</f>
-        <v/>
-      </c>
-      <c r="P9" s="9" t="inlineStr">
-        <is>
-          <t>Rivera et al. (2024)</t>
-        </is>
-      </c>
-      <c r="Q9" s="9" t="inlineStr">
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>CS3, CS10</t>
+        </is>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
         <is>
           <t>conflicts can escalate via destabilising dynamics (§3 intro).</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>Commitment and Trust</t>
         </is>
       </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>Evidence + text</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Paper prose</t>
+        </is>
+      </c>
+      <c r="E8" s="9">
+        <f>IF(F8*10=0,"—",IF(F8*10&gt;=9,"Strong",IF(F8*10&gt;=6,"Moderate",IF(F8*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="F8" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G8" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="9">
+        <f>IF(I8*10=0,"—",IF(I8*10&gt;=9,"Strong",IF(I8*10&gt;=6,"Moderate",IF(I8*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="I8" s="10" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="J8" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>Social Dilemmas
 Military Domains
 Coercion and Extortion</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr">
+      <c r="L8" s="9" t="inlineStr">
         <is>
           <t>Learning Peer and Pool Incentivisation
 Establishing Trust
@@ -2038,14 +1778,14 @@
 Evidential Reasoning</t>
         </is>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>Inefficient Outcomes
 Threats and Extortion
 Rigidity and Mistaken Commitments</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="N8" s="9" t="inlineStr">
         <is>
           <t>Keeping Humans in the Loop
 Limiting Commitment Power
@@ -2054,83 +1794,64 @@
 Mutual Simulation and Transparency</t>
         </is>
       </c>
-      <c r="J10" s="9" t="inlineStr">
-        <is>
-          <t>CS2: Common Resource Problems
-CS9: Cooperation Fails to Culturally Evolve among LLM Agents
-CS11: Dead Hands and Automated Deterrence</t>
-        </is>
-      </c>
-      <c r="K10" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" s="9" t="inlineStr">
-        <is>
-          <t>Literature
-Literature
-Historical example</t>
-        </is>
-      </c>
-      <c r="M10" s="9" t="inlineStr">
-        <is>
-          <t>Synthetic evidence
-Synthetic evidence
-Observed in real world</t>
-        </is>
-      </c>
-      <c r="N10" s="9">
-        <f>IF(O10=0,"—",IF(O10&gt;=9,"Strong",IF(O10&gt;=6,"Moderate",IF(O10&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="O10" s="10">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Commitment and Trust*")</f>
-        <v/>
-      </c>
-      <c r="P10" s="9" t="inlineStr">
-        <is>
-          <t>Piatti et al. (2024), GovSim
-Vallinder &amp; Hughes (2024)
-Hoffman (2009); Talbot (2005)</t>
-        </is>
-      </c>
-      <c r="Q10" s="9" t="inlineStr">
+      <c r="O8" s="9" t="inlineStr">
+        <is>
+          <t>CS2, CS9, CS11, AIV-06, AIV-05</t>
+        </is>
+      </c>
+      <c r="P8" s="9" t="inlineStr">
         <is>
           <t>Establishing Trust direction cross-refs §3.5; inability to commit is a major cause of costly conflict.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Multi-Agent Security</t>
         </is>
       </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>FALSE</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>Text cross-reference only</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>Paper prose</t>
+        </is>
+      </c>
+      <c r="E9" s="9">
+        <f>IF(F9*10=0,"—",IF(F9*10&gt;=9,"Strong",IF(F9*10&gt;=6,"Moderate",IF(F9*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="9">
+        <f>IF(I9*10=0,"—",IF(I9*10&gt;=9,"Strong",IF(I9*10&gt;=6,"Moderate",IF(I9*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="I9" s="10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>Social Dilemmas
 Military Domains
 Coercion and Extortion</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="L9" s="9" t="inlineStr">
         <is>
           <t>Learning Peer and Pool Incentivisation
 Establishing Trust
@@ -2140,7 +1861,7 @@
 Evidential Reasoning</t>
         </is>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>Swarm Attacks
 Heterogeneous Attacks
@@ -2150,7 +1871,7 @@
 Undetectable Threats</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="N9" s="9" t="inlineStr">
         <is>
           <t>Secure Interaction Protocols
 Monitoring and Threat Detection
@@ -2158,176 +1879,157 @@
 Sociotechnical Security Defences</t>
         </is>
       </c>
-      <c r="J11" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="9">
-        <f>IF(O11=0,"—",IF(O11&gt;=9,"Strong",IF(O11&gt;=6,"Moderate",IF(O11&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="O11" s="10">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*",Evidence!$K$2:$K$90,"*Multi-Agent Security*")</f>
-        <v/>
-      </c>
-      <c r="P11" s="9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Q11" s="9" t="inlineStr">
+      <c r="O9" s="9" t="inlineStr">
+        <is>
+          <t>CS5, CS8, CS12, CS13, AIR-2026-0193, AIR-2026-0189, AIR-2026-0183, AIR-2026-0180, LW-01, AIR-2026-0194, LW-02, AIR-2026-0219, AIR-2026-0101, AIR-2026-0029, AIR-2025-0177, AIR-2025-0149, AIR-2025-0136, AIR-2025-0070, AIR-2025-0068, AIR-2025-0027, AIR-2025-0019</t>
+        </is>
+      </c>
+      <c r="P9" s="9" t="inlineStr">
         <is>
           <t>Coercion and Extortion via hacking/jailbreaking other agents cross-refs §3.7.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="n">
+    <row r="10">
+      <c r="A10" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Collusion</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>Network Effects</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Paper prose</t>
+        </is>
+      </c>
+      <c r="E10" s="12">
+        <f>IF(F10*10=0,"—",IF(F10*10&gt;=9,"Strong",IF(F10*10&gt;=6,"Moderate",IF(F10*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="12">
+        <f>IF(I10*10=0,"—",IF(I10*10&gt;=9,"Strong",IF(I10*10&gt;=6,"Moderate",IF(I10*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="I10" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J10" s="14" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="11" t="inlineStr">
-        <is>
-          <t>Collusion</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
-        <is>
-          <t>Network Effects</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E12" s="11" t="inlineStr">
-        <is>
-          <t>Evidence + text</t>
-        </is>
-      </c>
-      <c r="F12" s="11" t="inlineStr">
+      <c r="K10" s="12" t="inlineStr">
         <is>
           <t>Markets
-Steganography</t>
-        </is>
-      </c>
-      <c r="G12" s="11" t="inlineStr">
+Steganography
+Defeating Oversight and Evaluation</t>
+        </is>
+      </c>
+      <c r="L10" s="12" t="inlineStr">
         <is>
           <t>Detecting AI Collusion
 Mitigating AI Collusion
 Assessing Impacts on Safety Protocols</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
+      <c r="M10" s="12" t="inlineStr">
         <is>
           <t>Error Propagation
 Network Rewiring
-Homogeneity and Correlated Failures</t>
-        </is>
-      </c>
-      <c r="I12" s="11" t="inlineStr">
+Homogeneity and Correlated Failures
+Informational Cascades</t>
+        </is>
+      </c>
+      <c r="N10" s="12" t="inlineStr">
         <is>
           <t>Evaluating and Monitoring Networks
 Faithful and Tractable Simulations
 Improving Network Security and Stability</t>
         </is>
       </c>
-      <c r="J12" s="11" t="inlineStr">
-        <is>
-          <t>LW-01: ExploitGym swarm and Hugging Face intrusion: about 1,200 agents in separate san…</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" s="11" t="inlineStr">
-        <is>
-          <t>Operator report</t>
-        </is>
-      </c>
-      <c r="M12" s="11" t="inlineStr">
-        <is>
-          <t>Observed in real world</t>
-        </is>
-      </c>
-      <c r="N12" s="11">
-        <f>IF(O12=0,"—",IF(O12&gt;=9,"Strong",IF(O12&gt;=6,"Moderate",IF(O12&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="O12" s="12">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*",Evidence!$K$2:$K$90,"*Network Effects*")</f>
-        <v/>
-      </c>
-      <c r="P12" s="11" t="inlineStr">
-        <is>
-          <t>OpenAI technical report</t>
-        </is>
-      </c>
-      <c r="Q12" s="11" t="inlineStr">
+      <c r="O10" s="12" t="inlineStr">
+        <is>
+          <t>CS7, CS8, CS10, AIV-07, AIR-2026-0193, AIR-2026-0189, LW-01, LW-05, AIV-03, AIR-2025-0068, AIV-01</t>
+        </is>
+      </c>
+      <c r="P10" s="12" t="inlineStr">
         <is>
           <t>AI-AI preferential attachment simulations cross-ref §2.3 (§3.2.3).</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Collusion</t>
         </is>
       </c>
-      <c r="C13" s="11" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Selection Pressures</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>Evidence</t>
-        </is>
-      </c>
-      <c r="F13" s="11" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Paper Table 3 co-tag</t>
+        </is>
+      </c>
+      <c r="E11" s="12">
+        <f>IF(F11*10=0,"—",IF(F11*10&gt;=9,"Strong",IF(F11*10&gt;=6,"Moderate",IF(F11*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H11" s="12">
+        <f>IF(I11*10=0,"—",IF(I11*10&gt;=9,"Strong",IF(I11*10&gt;=6,"Moderate",IF(I11*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="K11" s="12" t="inlineStr">
         <is>
           <t>Markets
-Steganography</t>
-        </is>
-      </c>
-      <c r="G13" s="11" t="inlineStr">
+Steganography
+Defeating Oversight and Evaluation</t>
+        </is>
+      </c>
+      <c r="L11" s="12" t="inlineStr">
         <is>
           <t>Detecting AI Collusion
 Mitigating AI Collusion
 Assessing Impacts on Safety Protocols</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
+      <c r="M11" s="12" t="inlineStr">
         <is>
           <t>Undesirable Dispositions from Competition
 Undesirable Dispositions from Human Data
 Undesirable Capabilities</t>
         </is>
       </c>
-      <c r="I13" s="11" t="inlineStr">
+      <c r="N11" s="12" t="inlineStr">
         <is>
           <t>Evaluating Against Diverse Co-Players
 Environment Design
@@ -2336,87 +2038,77 @@
 Simulating Selection Pressures</t>
         </is>
       </c>
-      <c r="J13" s="11" t="inlineStr">
-        <is>
-          <t>CS4: Algorithmic Collusion in the German Retail Gasoline Market</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>Historical example</t>
-        </is>
-      </c>
-      <c r="M13" s="11" t="inlineStr">
-        <is>
-          <t>Observed in real world</t>
-        </is>
-      </c>
-      <c r="N13" s="11">
-        <f>IF(O13=0,"—",IF(O13&gt;=9,"Strong",IF(O13&gt;=6,"Moderate",IF(O13&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="O13" s="12">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*",Evidence!$K$2:$K$90,"*Selection Pressures*")</f>
-        <v/>
-      </c>
-      <c r="P13" s="11" t="inlineStr">
-        <is>
-          <t>Assad et al. (2020)</t>
-        </is>
-      </c>
-      <c r="Q13" s="11" t="inlineStr">
+      <c r="O11" s="12" t="inlineStr">
+        <is>
+          <t>CS1, CS2, CS4, CS9</t>
+        </is>
+      </c>
+      <c r="P11" s="12" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Collusion</t>
         </is>
       </c>
-      <c r="C14" s="11" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Emergent Agency</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E14" s="11" t="inlineStr">
-        <is>
-          <t>Evidence + text</t>
-        </is>
-      </c>
-      <c r="F14" s="11" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Paper prose</t>
+        </is>
+      </c>
+      <c r="E12" s="12">
+        <f>IF(F12*10=0,"—",IF(F12*10&gt;=9,"Strong",IF(F12*10&gt;=6,"Moderate",IF(F12*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H12" s="12">
+        <f>IF(I12*10=0,"—",IF(I12*10&gt;=9,"Strong",IF(I12*10&gt;=6,"Moderate",IF(I12*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="I12" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K12" s="12" t="inlineStr">
         <is>
           <t>Markets
-Steganography</t>
-        </is>
-      </c>
-      <c r="G14" s="11" t="inlineStr">
+Steganography
+Defeating Oversight and Evaluation</t>
+        </is>
+      </c>
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t>Detecting AI Collusion
 Mitigating AI Collusion
 Assessing Impacts on Safety Protocols</t>
         </is>
       </c>
-      <c r="H14" s="11" t="inlineStr">
+      <c r="M12" s="12" t="inlineStr">
         <is>
           <t>Emergent Capabilities
 Emergent Goals</t>
         </is>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="N12" s="12" t="inlineStr">
         <is>
           <t>Empirical Exploration
 Theories of Emergent Capabilities
@@ -2424,93 +2116,71 @@
 Monitoring and Intervening on Collective Agents</t>
         </is>
       </c>
-      <c r="J14" s="11" t="inlineStr">
-        <is>
-          <t>CS4: Algorithmic Collusion in the German Retail Gasoline Market
-AIR-2026-0183: OpenAI evaluation agents turned an internal Artifactory service into a covert m…
-LW-01: ExploitGym swarm and Hugging Face intrusion: about 1,200 agents in separate san…
-AIR-2026-0219: A swarm of internally deployed OpenAI agents made more than 15,000 edits to the…</t>
-        </is>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L14" s="11" t="inlineStr">
-        <is>
-          <t>Historical example
-Safety failure
-Operator report
-Safety failure</t>
-        </is>
-      </c>
-      <c r="M14" s="11" t="inlineStr">
-        <is>
-          <t>Observed in real world
-Observed in real world
-Observed in real world
-Observed in real world</t>
-        </is>
-      </c>
-      <c r="N14" s="11">
-        <f>IF(O14=0,"—",IF(O14&gt;=9,"Strong",IF(O14&gt;=6,"Moderate",IF(O14&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="O14" s="12">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*",Evidence!$K$2:$K$90,"*Emergent Agency*")</f>
-        <v/>
-      </c>
-      <c r="P14" s="11" t="inlineStr">
-        <is>
-          <t>Assad et al. (2020)
-Agent Incident Registry (Enkrypt AI)
-OpenAI technical report
-Agent Incident Registry (Enkrypt AI)</t>
-        </is>
-      </c>
-      <c r="Q14" s="11" t="inlineStr">
+      <c r="O12" s="12" t="inlineStr">
+        <is>
+          <t>CS4, CS12, AIR-2026-0183, LW-01, AIR-2026-0219, LW-05, AIR-2025-0019</t>
+        </is>
+      </c>
+      <c r="P12" s="12" t="inlineStr">
         <is>
           <t>collusion can yield qualitatively new capabilities/goals (§2.3.2 → §3.6).</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Collusion</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>Multi-Agent Security</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>Evidence + text</t>
-        </is>
-      </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Paper prose</t>
+        </is>
+      </c>
+      <c r="E13" s="12">
+        <f>IF(F13*10=0,"—",IF(F13*10&gt;=9,"Strong",IF(F13*10&gt;=6,"Moderate",IF(F13*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="H13" s="12">
+        <f>IF(I13*10=0,"—",IF(I13*10&gt;=9,"Strong",IF(I13*10&gt;=6,"Moderate",IF(I13*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>21</v>
+      </c>
+      <c r="K13" s="12" t="inlineStr">
         <is>
           <t>Markets
-Steganography</t>
-        </is>
-      </c>
-      <c r="G15" s="11" t="inlineStr">
+Steganography
+Defeating Oversight and Evaluation</t>
+        </is>
+      </c>
+      <c r="L13" s="12" t="inlineStr">
         <is>
           <t>Detecting AI Collusion
 Mitigating AI Collusion
 Assessing Impacts on Safety Protocols</t>
         </is>
       </c>
-      <c r="H15" s="11" t="inlineStr">
+      <c r="M13" s="12" t="inlineStr">
         <is>
           <t>Swarm Attacks
 Heterogeneous Attacks
@@ -2520,7 +2190,7 @@
 Undetectable Threats</t>
         </is>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="N13" s="12" t="inlineStr">
         <is>
           <t>Secure Interaction Protocols
 Monitoring and Threat Detection
@@ -2528,61 +2198,29 @@
 Sociotechnical Security Defences</t>
         </is>
       </c>
-      <c r="J15" s="11" t="inlineStr">
-        <is>
-          <t>CS5: Language Model Steganography
-AIR-2026-0183: OpenAI evaluation agents turned an internal Artifactory service into a covert m…
-LW-01: ExploitGym swarm and Hugging Face intrusion: about 1,200 agents in separate san…
-LW-02: Vanderbilt link shortener operation: a swarm used public link-shortener statist…
-AIR-2026-0219: A swarm of internally deployed OpenAI agents made more than 15,000 edits to the…</t>
-        </is>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L15" s="11" t="inlineStr">
-        <is>
-          <t>Literature
-Safety failure
-Operator report
-Independent investigation
-Safety failure</t>
-        </is>
-      </c>
-      <c r="M15" s="11" t="inlineStr">
-        <is>
-          <t>Observed in lab
-Observed in real world
-Observed in real world
-Observed in real world
-Observed in real world</t>
-        </is>
-      </c>
-      <c r="N15" s="11">
-        <f>IF(O15=0,"—",IF(O15&gt;=9,"Strong",IF(O15&gt;=6,"Moderate",IF(O15&gt;=3,"Limited","Weak"))))</f>
-        <v/>
-      </c>
-      <c r="O15" s="12">
-        <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*",Evidence!$K$2:$K$90,"*Multi-Agent Security*")</f>
-        <v/>
-      </c>
-      <c r="P15" s="11" t="inlineStr">
-        <is>
-          <t>Motwani et al. (2024)
-Agent Incident Registry (Enkrypt AI)
-OpenAI technical report
-DeGraff: swarm investigation
-Agent Incident Registry (Enkrypt AI)</t>
-        </is>
-      </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="O13" s="12" t="inlineStr">
+        <is>
+          <t>CS5, CS8, CS12, CS13, AIR-2026-0193, AIR-2026-0189, AIR-2026-0183, AIR-2026-0180, LW-01, AIR-2026-0194, LW-02, AIR-2026-0219, AIR-2026-0101, AIR-2026-0029, AIR-2025-0177, AIR-2025-0149, AIR-2025-0136, AIR-2025-0070, AIR-2025-0068, AIR-2025-0027, AIR-2025-0019</t>
+        </is>
+      </c>
+      <c r="P13" s="12" t="inlineStr">
         <is>
           <t>collusion to bypass safeguards; Assessing Impacts on Safety Protocols cross-refs §3.6–3.7.</t>
         </is>
       </c>
     </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Evidence attaches to a single-risk instance, never to a pair. A failure mode is grounded by its own evidence; rf_grounding_amplifying is the linked risk factor's grounding routed along an author-asserted link, not evidence that this factor produced this failure.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q15"/>
+  <autoFilter ref="A1:P13"/>
+  <mergeCells count="1">
+    <mergeCell ref="A15:J15"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2703,7 +2341,8 @@
         <is>
           <t>Incompatible Strategies
 Credit Assignment
-Limited Interactions</t>
+Limited Interactions
+Shared False Beliefs</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -2716,10 +2355,8 @@
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Information Asymmetries
-Network Effects
 Selection Pressures
-Destabilising Dynamics
-Commitment and Trust</t>
+Destabilising Dynamics</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -2820,7 +2457,7 @@
 CS11: Dead Hands and Automated Deterrence</t>
         </is>
       </c>
-      <c r="I3" s="10" t="n">
+      <c r="I3" s="11" t="n">
         <v>5</v>
       </c>
       <c r="J3" s="9" t="inlineStr">
@@ -2845,46 +2482,47 @@
         <f>IF(M3=0,"—",IF(M3&gt;=9,"Strong",IF(M3&gt;=6,"Moderate",IF(M3&gt;=3,"Limited","Weak"))))</f>
         <v/>
       </c>
-      <c r="M3" s="10">
+      <c r="M3" s="11">
         <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Conflict*")</f>
         <v/>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Failure mode</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Collusion</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="12" t="inlineStr">
         <is>
           <t>2.3</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="12" t="inlineStr">
         <is>
           <t>Undesired (often covert) cooperation between AI systems at the expense of third parties, e.g. markets or oversight schemes.</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="12" t="inlineStr">
         <is>
           <t>Markets
-Steganography</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
+Steganography
+Defeating Oversight and Evaluation</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>Detecting AI Collusion
 Mitigating AI Collusion
 Assessing Impacts on Safety Protocols</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="12" t="inlineStr">
         <is>
           <t>Network Effects
 Selection Pressures
@@ -2892,7 +2530,7 @@
 Multi-Agent Security</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="12" t="inlineStr">
         <is>
           <t>CS4: Algorithmic Collusion in the German Retail Gasoline Market
 CS5: Language Model Steganography
@@ -2902,10 +2540,10 @@
 AIR-2026-0219: A swarm of internally deployed OpenAI agents made more than 15,000 edits to the…</t>
         </is>
       </c>
-      <c r="I4" s="12" t="n">
+      <c r="I4" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="12" t="inlineStr">
         <is>
           <t>Historical example
 Literature
@@ -2915,7 +2553,7 @@
 Safety failure</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="12" t="inlineStr">
         <is>
           <t>Observed in real world
 Observed in lab
@@ -2925,11 +2563,11 @@
 Observed in real world</t>
         </is>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="12">
         <f>IF(M4=0,"—",IF(M4&gt;=9,"Strong",IF(M4&gt;=6,"Moderate",IF(M4&gt;=3,"Limited","Weak"))))</f>
         <v/>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="14">
         <f>_xlfn.MAXIFS(Evidence!$M$2:$M$90,Evidence!$J$2:$J$90,"*Collusion*")</f>
         <v/>
       </c>
@@ -2984,14 +2622,11 @@
 AIV-07: DeepSeek-V3.2 persuasion campaign: invented a self-serving metric; the group ad…
 AIV-06: Agents finetune their own leader: Opus assumed GPT-5.5 agreed without confirmin…
 AIV-05: Sabotage game: saboteurs tried to hide easter eggs in a shared game; Opus 4.6 e…
-AIR-2025-0149: OpenAI Agent Builder: a poisoned lead-form submission redirects a multi-agent s…
-AIV-03: Game-choice herding: agents copied the games peers announced they were beating…
-AIV-01: Hallucinated mailing list spreads between agents: o3 invented a 93-person maili…
-AIV-02: False 'broken UI' belief spreads: Gemini 2.5 Pro logged its own misclicks as sy…</t>
+AIR-2025-0149: OpenAI Agent Builder: a poisoned lead-form submission redirects a multi-agent s…</t>
         </is>
       </c>
       <c r="I5" s="7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
@@ -3001,10 +2636,7 @@
 Operator blog
 Operator blog
 Operator blog
-Research demo
-Operator blog
-Operator blog
-Operator blog</t>
+Research demo</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -3015,10 +2647,7 @@
 Synthetic evidence
 Synthetic evidence
 Synthetic evidence
-Observed in lab
-Synthetic evidence
-Synthetic evidence
-Synthetic evidence</t>
+Observed in lab</t>
         </is>
       </c>
       <c r="L5" s="5">
@@ -3055,7 +2684,8 @@
         <is>
           <t>Error Propagation
 Network Rewiring
-Homogeneity and Correlated Failures</t>
+Homogeneity and Correlated Failures
+Informational Cascades</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
@@ -3067,8 +2697,7 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Miscoordination
-Collusion</t>
+          <t>Collusion</t>
         </is>
       </c>
       <c r="H6" s="5" t="inlineStr">
@@ -3320,8 +2949,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Miscoordination
-Conflict</t>
+          <t>Conflict</t>
         </is>
       </c>
       <c r="H9" s="5" t="inlineStr">
@@ -3329,28 +2957,20 @@
           <t>CS2: Common Resource Problems
 CS9: Cooperation Fails to Culturally Evolve among LLM Agents
 CS11: Dead Hands and Automated Deterrence
-AIR-2026-0180: 'I'll just call you': a low-privileged CI agent on Google's adk-python is injec…
 AIV-06: Agents finetune their own leader: Opus assumed GPT-5.5 agreed without confirmin…
-AIR-2026-0101: Morse-code prompt injection made Grok relay a transfer instruction to Bankrbot,…
-AIV-05: Sabotage game: saboteurs tried to hide easter eggs in a shared game; Opus 4.6 e…
-AIR-2025-0177: ServiceNow Now Assist: second-order prompt injection recruits privileged agents…
-AIR-2025-0136: Cross-agent privilege escalation: one hijacked coding agent rewrites another ag…</t>
+AIV-05: Sabotage game: saboteurs tried to hide easter eggs in a shared game; Opus 4.6 e…</t>
         </is>
       </c>
       <c r="I9" s="7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Literature
 Literature
 Historical example
-Disclosed vulnerability
 Operator blog
-In the wild
-Operator blog
-Disclosed vulnerability
-Disclosed vulnerability</t>
+Operator blog</t>
         </is>
       </c>
       <c r="K9" s="5" t="inlineStr">
@@ -3358,12 +2978,8 @@
           <t>Synthetic evidence
 Synthetic evidence
 Observed in real world
-Observed in lab
 Synthetic evidence
-Observed in real world
-Synthetic evidence
-Observed in lab
-Observed in lab</t>
+Synthetic evidence</t>
         </is>
       </c>
       <c r="L9" s="5">
@@ -3423,12 +3039,11 @@
 LW-01: ExploitGym swarm and Hugging Face intrusion: about 1,200 agents in separate san…
 AIR-2026-0219: A swarm of internally deployed OpenAI agents made more than 15,000 edits to the…
 LW-05: Moltbook agent behaviour: AI-agent-only social network reportedly reached ~36k…
-AIR-2025-0027: Influence-as-a-service: Claude used as the orchestrator deciding actions for 10…
 AIR-2025-0019: Xanthorox AI: a self-hosted, five-model offensive platform sold on darknet foru…</t>
         </is>
       </c>
       <c r="I10" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
@@ -3438,7 +3053,6 @@
 Operator report
 Safety failure
 Forum post
-In the wild
 In the wild</t>
         </is>
       </c>
@@ -3446,7 +3060,6 @@
         <is>
           <t>Observed in real world
 Observed in lab
-Observed in real world
 Observed in real world
 Observed in real world
 Observed in real world
@@ -3529,11 +3142,12 @@
 AIR-2025-0136: Cross-agent privilege escalation: one hijacked coding agent rewrites another ag…
 AIR-2025-0070: PajaMAS: hijacking multi-agent systems built on Google's Agent Development Kit
 AIR-2025-0068: IdentityMesh: agentic lateral movement through merged identities across connect…
+AIR-2025-0027: Influence-as-a-service: Claude used as the orchestrator deciding actions for 10…
 AIR-2025-0019: Xanthorox AI: a self-hosted, five-model offensive platform sold on darknet foru…</t>
         </is>
       </c>
       <c r="I11" s="7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
@@ -3556,6 +3170,7 @@
 Disclosed vulnerability
 Research demo
 Research demo
+In the wild
 In the wild</t>
         </is>
       </c>
@@ -3580,6 +3195,7 @@
 Observed in lab
 Observed in lab
 Observed in lab
+Observed in real world
 Observed in real world</t>
         </is>
       </c>
@@ -3604,7 +3220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3612,12 +3228,16 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="36" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -3648,30 +3268,50 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>evidence_explicit</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>evidence_placement</t>
+          <t>evidence_basis</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>evidence_basis</t>
+          <t>evidence</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>evidence_score_max</t>
+          <t>evidence_n</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>evidence_strength_max</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>instance_grounding</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>paper_cross_ref_explicit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>paper_cross_ref_placement</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>key_references</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>support_summary</t>
         </is>
@@ -3705,29 +3345,45 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>CS1, AIV-06, AIV-04</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2" s="5">
+        <f>IF(K2*10=0,"—",IF(K2*10&gt;=9,"Strong",IF(K2*10&gt;=6,"Moderate",IF(K2*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K2" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
           <t>CS1</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H2" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I2" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS1",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3761,26 +3417,45 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G3" s="15" t="inlineStr">
+        <is>
+          <t>Cited empirical work</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="I3" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
+        <f>IF(K3*10=0,"—",IF(K3*10&gt;=9,"Strong",IF(K3*10&gt;=6,"Moderate",IF(K3*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H3" s="13" t="inlineStr">
-        <is>
-          <t>Cited empirical work</t>
-        </is>
-      </c>
-      <c r="I3" s="7" t="n"/>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Du et al. 2023; Li et al. 2025; Agapiou et al. 2022</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Known multi-agent learning problem: unclear which agent caused an outcome; agents must generalise to unfamiliar co-players.</t>
         </is>
@@ -3814,26 +3489,45 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G4" s="15" t="inlineStr">
+        <is>
+          <t>Cited empirical work</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="I4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <f>IF(K4*10=0,"—",IF(K4*10&gt;=9,"Strong",IF(K4*10&gt;=6,"Moderate",IF(K4*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H4" s="13" t="inlineStr">
-        <is>
-          <t>Cited empirical work</t>
-        </is>
-      </c>
-      <c r="I4" s="7" t="n"/>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Hu et al. 2020; Treutlein et al. 2021; Emmons et al. 2022</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>Zero- and few-shot coordination research: without shared history or communication, agents must coordinate blind.</t>
         </is>
@@ -3867,29 +3561,45 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G5" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>CS2, CS6, CS9</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="5">
+        <f>IF(K5*10=0,"—",IF(K5*10&gt;=9,"Strong",IF(K5*10&gt;=6,"Moderate",IF(K5*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
           <t>CS10</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>CS2</t>
         </is>
       </c>
-      <c r="H5" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I5" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS10",Evidence!$A$2:$A$90,0)),INDEX(Evidence!$M$2:$M$90,MATCH("CS2",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3923,29 +3633,45 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>CS3</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="5">
+        <f>IF(K6*10=0,"—",IF(K6*10&gt;=9,"Strong",IF(K6*10&gt;=6,"Moderate",IF(K6*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L6" s="5" t="inlineStr">
+        <is>
           <t>CS10</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>CS3</t>
         </is>
       </c>
-      <c r="H6" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I6" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS10",Evidence!$A$2:$A$90,0)),INDEX(Evidence!$M$2:$M$90,MATCH("CS3",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -3979,26 +3705,45 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G7" s="16" t="inlineStr">
+        <is>
+          <t>Theoretical</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>CS11</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="5">
+        <f>IF(K7*10=0,"—",IF(K7*10&gt;=9,"Strong",IF(K7*10&gt;=6,"Moderate",IF(K7*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>Theoretical</t>
-        </is>
-      </c>
-      <c r="I7" s="7" t="n"/>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Ellsberg 1968; Harrenstein et al. 2007</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Argued: AI cyber-offence and surveillance make threats cheaper, more widespread and harder to detect.</t>
         </is>
@@ -4032,29 +3777,45 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G8" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>CS4</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="5">
+        <f>IF(K8*10=0,"—",IF(K8*10&gt;=9,"Strong",IF(K8*10&gt;=6,"Moderate",IF(K8*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K8" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
           <t>CS4, CS10</t>
         </is>
       </c>
-      <c r="G8" s="5" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H8" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I8" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS4",Evidence!$A$2:$A$90,0)),INDEX(Evidence!$M$2:$M$90,MATCH("CS10",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="O8" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4088,29 +3849,45 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
           <t>CS5</t>
         </is>
       </c>
-      <c r="G9" s="5" t="inlineStr">
+      <c r="I9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="5">
+        <f>IF(K9*10=0,"—",IF(K9*10&gt;=9,"Strong",IF(K9*10&gt;=6,"Moderate",IF(K9*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>CS5</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H9" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I9" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS5",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4144,26 +3921,45 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G10" s="15" t="inlineStr">
+        <is>
+          <t>Cited empirical work</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>CS1, AIV-06</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="5">
+        <f>IF(K10*10=0,"—",IF(K10*10&gt;=9,"Strong",IF(K10*10&gt;=6,"Moderate",IF(K10*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K10" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="5" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="13" t="inlineStr">
-        <is>
-          <t>Cited empirical work</t>
-        </is>
-      </c>
-      <c r="I10" s="7" t="n"/>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>Foerster et al. 2016; Lazaridou &amp; Baroni 2020; Sukhbaatar et al. 2016</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="O10" s="5" t="inlineStr">
         <is>
           <t>Emergent-communication research on constrained channels; strategic withholding expected to dominate as capabilities grow.</t>
         </is>
@@ -4197,26 +3993,45 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G11" s="16" t="inlineStr">
+        <is>
+          <t>Theoretical</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="5" t="inlineStr">
+      <c r="I11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <f>IF(K11*10=0,"—",IF(K11*10&gt;=9,"Strong",IF(K11*10&gt;=6,"Moderate",IF(K11*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>Theoretical</t>
-        </is>
-      </c>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>Myerson &amp; Satterthwaite 1983; Fearon 1995</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>Formal results: private valuations make efficient bargaining impossible to guarantee and can lead to costly conflict.</t>
         </is>
@@ -4250,29 +4065,45 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>CS6, CS7, AIV-07, AIV-05, AIR-2025-0149</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" s="5">
+        <f>IF(K12*10=0,"—",IF(K12*10&gt;=9,"Strong",IF(K12*10&gt;=6,"Moderate",IF(K12*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L12" s="5" t="inlineStr">
+        <is>
           <t>CS7</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>CS6</t>
         </is>
       </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I12" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS7",Evidence!$A$2:$A$90,0)),INDEX(Evidence!$M$2:$M$90,MATCH("CS6",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="O12" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4306,29 +4137,45 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>CS7, CS8, CS10, AIV-07, AIR-2026-0193, AIV-01</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J13" s="5">
+        <f>IF(K13*10=0,"—",IF(K13*10&gt;=9,"Strong",IF(K13*10&gt;=6,"Moderate",IF(K13*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
           <t>CS7, CS8</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H13" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I13" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS7",Evidence!$A$2:$A$90,0)),INDEX(Evidence!$M$2:$M$90,MATCH("CS8",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="O13" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4362,26 +4209,45 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>Theoretical</t>
+        </is>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>AIR-2026-0189, LW-05, AIR-2025-0068</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="5">
+        <f>IF(K14*10=0,"—",IF(K14*10&gt;=9,"Strong",IF(K14*10&gt;=6,"Moderate",IF(K14*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L14" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G14" s="5" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>Theoretical</t>
-        </is>
-      </c>
-      <c r="I14" s="7" t="n"/>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>Albert et al. 2000; Kunegis et al. 2013</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="O14" s="5" t="inlineStr">
         <is>
           <t>Network theory: AI-AI preferential attachment could centralise AI nodes or trigger phase transitions. Only anecdote cited (forum bots, Kulveit 2023).</t>
         </is>
@@ -4415,26 +4281,45 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G15" s="16" t="inlineStr">
+        <is>
+          <t>Theoretical</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>LW-01</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="5">
+        <f>IF(K15*10=0,"—",IF(K15*10&gt;=9,"Strong",IF(K15*10&gt;=6,"Moderate",IF(K15*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L15" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>Theoretical</t>
-        </is>
-      </c>
-      <c r="I15" s="7" t="n"/>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>Bommasani et al. 2021</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>Argued: many agents built on few foundation models share failure modes, vulnerabilities and biases.</t>
         </is>
@@ -4468,29 +4353,45 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>CS1, CS2, CS4, CS9</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" s="5">
+        <f>IF(K16*10=0,"—",IF(K16*10&gt;=9,"Strong",IF(K16*10&gt;=6,"Moderate",IF(K16*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G16" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>CS9</t>
         </is>
       </c>
-      <c r="H16" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I16" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS9",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="O16" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4524,29 +4425,45 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <f>IF(K17*10=0,"—",IF(K17*10&gt;=9,"Strong",IF(K17*10&gt;=6,"Moderate",IF(K17*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
           <t>CS7</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H17" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I17" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS7",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="O17" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4580,26 +4497,45 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Cited empirical work</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="I18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5">
+        <f>IF(K18*10=0,"—",IF(K18*10&gt;=9,"Strong",IF(K18*10&gt;=6,"Moderate",IF(K18*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>Cited empirical work</t>
-        </is>
-      </c>
-      <c r="I18" s="7" t="n"/>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>Baker et al. 2019; Blumenkamp &amp; Prorok 2021</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="O18" s="5" t="inlineStr">
         <is>
           <t>Co-adaptation autocurricula: emergent tool use in hide-and-seek; agents learning manipulative communication.</t>
         </is>
@@ -4633,29 +4569,45 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>CS3, CS10</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="5">
+        <f>IF(K19*10=0,"—",IF(K19*10&gt;=9,"Strong",IF(K19*10&gt;=6,"Moderate",IF(K19*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
           <t>CS10</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H19" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I19" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS10",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -4689,26 +4641,45 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G20" s="16" t="inlineStr">
+        <is>
+          <t>Theoretical</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
+      <c r="I20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5">
+        <f>IF(K20*10=0,"—",IF(K20*10&gt;=9,"Strong",IF(K20*10&gt;=6,"Moderate",IF(K20*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K20" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>Theoretical</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="n"/>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>Zinkevich et al. 2005; Paes Leme et al. 2024</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="O20" s="5" t="inlineStr">
         <is>
           <t>Formal results: multi-agent Q-learning can cycle; auto-bidding dynamics can fail to converge to truthful equilibria.</t>
         </is>
@@ -4742,26 +4713,45 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G21" s="16" t="inlineStr">
+        <is>
+          <t>Theoretical</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="5" t="inlineStr">
+      <c r="I21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5">
+        <f>IF(K21*10=0,"—",IF(K21*10&gt;=9,"Strong",IF(K21*10&gt;=6,"Moderate",IF(K21*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>Theoretical</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="n"/>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>Sanders et al. 2018; Cheung &amp; Piliouras 2020</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>Formal results: chaotic learning dynamics become the norm as agent count grows; paper notes not yet seen in frontier AI.</t>
         </is>
@@ -4795,26 +4785,45 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G22" s="16" t="inlineStr">
+        <is>
+          <t>Theoretical</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr">
+      <c r="I22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="5">
+        <f>IF(K22*10=0,"—",IF(K22*10&gt;=9,"Strong",IF(K22*10&gt;=6,"Moderate",IF(K22*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>Theoretical</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="n"/>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>Leonardos &amp; Piliouras 2022; Zeeman 1976</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>Formal results: small parameter changes (e.g. RL exploration rate) cause bifurcations in equilibria.</t>
         </is>
@@ -4848,26 +4857,45 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G23" s="16" t="inlineStr">
+        <is>
+          <t>Theoretical</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="I23" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5">
+        <f>IF(K23*10=0,"—",IF(K23*10&gt;=9,"Strong",IF(K23*10&gt;=6,"Moderate",IF(K23*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>Theoretical</t>
-        </is>
-      </c>
-      <c r="I23" s="7" t="n"/>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>Stastny et al. 2021; Papoudakis et al. 2019</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>Argued: co-adapting agents create non-stationarity; narrow training co-players cause overconfidence in negotiation.</t>
         </is>
@@ -4901,26 +4929,45 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G24" s="16" t="inlineStr">
+        <is>
+          <t>Theoretical</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>CS2, CS9, AIV-06</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J24" s="5">
+        <f>IF(K24*10=0,"—",IF(K24*10&gt;=9,"Strong",IF(K24*10&gt;=6,"Moderate",IF(K24*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
+      <c r="M24" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>Theoretical</t>
-        </is>
-      </c>
-      <c r="I24" s="7" t="n"/>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>Fearon 1995; Powell 2006</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>Argued: easily created, deceptive agents garner little trust, causing economic inefficiency and pressure to defect.</t>
         </is>
@@ -4954,29 +5001,45 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
           <t>CS11</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
+      <c r="I25" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" s="5">
+        <f>IF(K25*10=0,"—",IF(K25*10&gt;=9,"Strong",IF(K25*10&gt;=6,"Moderate",IF(K25*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K25" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>CS11</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I25" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS11",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5010,29 +5073,45 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>CS11, AIV-05</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J26" s="5">
+        <f>IF(K26*10=0,"—",IF(K26*10&gt;=9,"Strong",IF(K26*10&gt;=6,"Moderate",IF(K26*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
           <t>CS11</t>
         </is>
       </c>
-      <c r="G26" s="5" t="inlineStr">
+      <c r="M26" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I26" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS11",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="N26" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="O26" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5066,26 +5145,45 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>Theoretical</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>CS4, CS12, AIR-2026-0183, LW-01, AIR-2026-0219, AIR-2025-0019</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" s="5">
+        <f>IF(K27*10=0,"—",IF(K27*10&gt;=9,"Strong",IF(K27*10&gt;=6,"Moderate",IF(K27*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G27" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>Theoretical</t>
-        </is>
-      </c>
-      <c r="I27" s="7" t="n"/>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>Konda &amp; Tsitsiklis 2000; Drexler 2019</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="O27" s="5" t="inlineStr">
         <is>
           <t>Hypothetical: composed narrow tools (e.g. automated chemistry workflow) exceed individual capabilities. CS12 gives partial lab evidence.</t>
         </is>
@@ -5119,26 +5217,45 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>Theoretical</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>LW-05</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" s="5">
+        <f>IF(K28*10=0,"—",IF(K28*10&gt;=9,"Strong",IF(K28*10&gt;=6,"Moderate",IF(K28*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="M28" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H28" s="14" t="inlineStr">
-        <is>
-          <t>Theoretical</t>
-        </is>
-      </c>
-      <c r="I28" s="7" t="n"/>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>Dennett 1971</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="O28" s="5" t="inlineStr">
         <is>
           <t>Hypothetical: engagement-optimising moderation bots collectively shift users' politics. Paper states no advanced-AI examples are known.</t>
         </is>
@@ -5172,26 +5289,45 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>Theoretical</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>AIR-2026-0189, AIR-2026-0183, LW-01, AIR-2026-0194, LW-02, AIR-2026-0219, AIR-2025-0019</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="J29" s="5">
+        <f>IF(K29*10=0,"—",IF(K29*10&gt;=9,"Strong",IF(K29*10&gt;=6,"Moderate",IF(K29*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G29" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H29" s="14" t="inlineStr">
-        <is>
-          <t>Theoretical</t>
-        </is>
-      </c>
-      <c r="I29" s="7" t="n"/>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>DDoS / brigading analogues (Cisco 2023)</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="O29" s="5" t="inlineStr">
         <is>
           <t>Extrapolated from non-AI bot swarms to adaptive AI agents that jointly find new attack surfaces.</t>
         </is>
@@ -5225,29 +5361,45 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
           <t>CS12</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="I30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" s="5">
+        <f>IF(K30*10=0,"—",IF(K30*10&gt;=9,"Strong",IF(K30*10&gt;=6,"Moderate",IF(K30*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>CS12</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I30" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS12",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="O30" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5281,26 +5433,45 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>Theoretical</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>AIR-2025-0027</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" s="5">
+        <f>IF(K31*10=0,"—",IF(K31*10&gt;=9,"Strong",IF(K31*10&gt;=6,"Moderate",IF(K31*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K31" s="6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H31" s="14" t="inlineStr">
-        <is>
-          <t>Theoretical</t>
-        </is>
-      </c>
-      <c r="I31" s="7" t="n"/>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>Ai et al. 2024; Hazell 2023</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="O31" s="5" t="inlineStr">
         <is>
           <t>Argued: many coordinated, seemingly independent agents persuade or phish more effectively and evade detection.</t>
         </is>
@@ -5334,29 +5505,45 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>CS13, AIR-2026-0180, AIR-2026-0101, AIR-2026-0029, AIR-2025-0177, AIR-2025-0149, AIR-2025-0136, AIR-2025-0070</t>
+        </is>
+      </c>
+      <c r="I32" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" s="5">
+        <f>IF(K32*10=0,"—",IF(K32*10&gt;=9,"Strong",IF(K32*10&gt;=6,"Moderate",IF(K32*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K32" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
           <t>CS13</t>
         </is>
       </c>
-      <c r="G32" s="5" t="inlineStr">
+      <c r="M32" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I32" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS13",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="O32" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5390,29 +5577,45 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>Case study</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>CS8, AIR-2026-0193, AIR-2025-0068</t>
+        </is>
+      </c>
+      <c r="I33" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="5">
+        <f>IF(K33*10=0,"—",IF(K33*10&gt;=9,"Strong",IF(K33*10&gt;=6,"Moderate",IF(K33*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K33" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
           <t>CS8</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
-        <is>
-          <t>Case study</t>
-        </is>
-      </c>
-      <c r="I33" s="7">
-        <f>MAX(INDEX(Evidence!$M$2:$M$90,MATCH("CS8",Evidence!$A$2:$A$90,0)))</f>
-        <v/>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="O33" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -5446,33 +5649,268 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
+          <t>Hammond Table 1</t>
+        </is>
+      </c>
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>Cited empirical work</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>CS5</t>
+        </is>
+      </c>
+      <c r="I34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" s="5">
+        <f>IF(K34*10=0,"—",IF(K34*10&gt;=9,"Strong",IF(K34*10&gt;=6,"Moderate",IF(K34*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K34" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G34" s="5" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H34" s="13" t="inlineStr">
-        <is>
-          <t>Cited empirical work</t>
-        </is>
-      </c>
-      <c r="I34" s="7" t="n"/>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>Motwani et al. 2024; Franzmeyer et al. 2023; Draguns et al. 2024</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>Steganography, illusory attacks and encrypted backdoors shown to evade detection. Motwani et al. is also the CS5 source but is not cross-referenced here as a case study.</t>
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>I34</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Shared False Beliefs</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Miscoordination</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>Incident evidence</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>AIV-07, AIV-01, AIV-02</t>
+        </is>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" s="5">
+        <f>IF(K35*10=0,"—",IF(K35*10&gt;=9,"Strong",IF(K35*10&gt;=6,"Moderate",IF(K35*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O35" s="5" t="inlineStr">
+        <is>
+          <t>A false belief originating with one agent is adopted by others and acted on, so a group with a common objective coordinates on something untrue. Authored because Hammond's FM1 instances (Incompatible Strategies, Credit Assignment, Limited Interactions) do not cover belief contagion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>I35</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Defeating Oversight and Evaluation</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Collusion</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Failure mode</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>2.3</t>
+        </is>
+      </c>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Incident evidence</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>AIR-2026-0183, LW-01, LW-02, AIR-2026-0219</t>
+        </is>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J36" s="5">
+        <f>IF(K36*10=0,"—",IF(K36*10&gt;=9,"Strong",IF(K36*10&gt;=6,"Moderate",IF(K36*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O36" s="5" t="inlineStr">
+        <is>
+          <t>Agents cooperate, usually covertly, to subvert an evaluation, scorer or monitoring scheme. Authored because FM3's definition names oversight schemes but Table 1 instantiates only Markets and Steganography.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>I36</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Informational Cascades</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Network Effects</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Risk factor</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Ours</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Incident evidence</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>AIV-03</t>
+        </is>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" s="5">
+        <f>IF(K37*10=0,"—",IF(K37*10&gt;=9,"Strong",IF(K37*10&gt;=6,"Moderate",IF(K37*10&gt;=3,"Limited","Weak"))))</f>
+        <v/>
+      </c>
+      <c r="K37" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O37" s="5" t="inlineStr">
+        <is>
+          <t>Agents copy peers' observed choices in place of their own assessment, so one agent's pick propagates through the group. Distinct from Error Propagation, which carries a falsity rather than a choice.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:K34"/>
+  <autoFilter ref="A1:O37"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5635,1288 +6073,1288 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>CS1</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Case study</t>
         </is>
       </c>
-      <c r="C2" s="14" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>Zero-Shot Coordination Failures in Driving</t>
         </is>
       </c>
-      <c r="D2" s="15" t="n">
+      <c r="D2" s="17" t="n">
         <v>45707</v>
       </c>
-      <c r="E2" s="14" t="inlineStr">
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>Synthetic evidence</t>
         </is>
       </c>
-      <c r="F2" s="14" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>Novel experiment by report authors</t>
         </is>
       </c>
-      <c r="G2" s="14" t="n"/>
-      <c r="H2" s="14" t="inlineStr">
+      <c r="G2" s="16" t="n"/>
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>Advanced AI agents</t>
         </is>
       </c>
-      <c r="I2" s="14" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>No realized harm flag</t>
         </is>
       </c>
-      <c r="J2" s="14" t="inlineStr">
+      <c r="J2" s="16" t="inlineStr">
         <is>
           <t>Miscoordination</t>
         </is>
       </c>
-      <c r="K2" s="14" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>Information Asymmetries
 Selection Pressures</t>
         </is>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="16">
         <f>IF(M2&gt;=9,"Strong",IF(M2&gt;=6,"Moderate",IF(M2&gt;=3,"Limited","Weak")))</f>
         <v/>
       </c>
-      <c r="M2" s="16">
+      <c r="M2" s="18">
         <f>SUM(N2:R2)</f>
         <v/>
       </c>
-      <c r="N2" s="16" t="n">
+      <c r="N2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="O2" s="16" t="n">
+      <c r="O2" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="P2" s="16" t="n">
+      <c r="P2" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="Q2" s="16" t="n">
+      <c r="Q2" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="R2" s="16" t="n">
+      <c r="R2" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S2" s="14" t="inlineStr">
+      <c r="S2" s="16" t="inlineStr">
         <is>
           <t>Base vs specialised comparison; n=40; report-authored, unreviewed. Text scene descriptions of driving situations; no physics sim.</t>
         </is>
       </c>
-      <c r="T2" s="14" t="n">
+      <c r="T2" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="U2" s="14" t="inlineStr">
+      <c r="U2" s="16" t="inlineStr">
         <is>
           <t>Report authors (App. B.1)</t>
         </is>
       </c>
-      <c r="V2" s="17" t="inlineStr">
+      <c r="V2" s="19" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2502.14143</t>
         </is>
       </c>
-      <c r="W2" s="15" t="n">
+      <c r="W2" s="17" t="n">
         <v>46320</v>
       </c>
-      <c r="X2" s="14" t="inlineStr">
+      <c r="X2" s="16" t="inlineStr">
         <is>
           <t>Two GPT-3.5 agents fine-tuned on US vs Indian emergency-yielding conventions failed 77.5% of scenarios (31/40) vs 5% for base models.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>CS2</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Case study</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="16" t="inlineStr">
         <is>
           <t>Common Resource Problems</t>
         </is>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="D3" s="20" t="n">
         <v>45292</v>
       </c>
-      <c r="E3" s="14" t="inlineStr">
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>Synthetic evidence</t>
         </is>
       </c>
-      <c r="F3" s="14" t="inlineStr">
+      <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Literature</t>
         </is>
       </c>
-      <c r="G3" s="14" t="n"/>
-      <c r="H3" s="14" t="inlineStr">
+      <c r="G3" s="16" t="n"/>
+      <c r="H3" s="16" t="inlineStr">
         <is>
           <t>Advanced AI agents</t>
         </is>
       </c>
-      <c r="I3" s="14" t="inlineStr">
+      <c r="I3" s="16" t="inlineStr">
         <is>
           <t>No realized harm flag</t>
         </is>
       </c>
-      <c r="J3" s="14" t="inlineStr">
+      <c r="J3" s="16" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="K3" s="14" t="inlineStr">
+      <c r="K3" s="16" t="inlineStr">
         <is>
           <t>Selection Pressures
 Commitment and Trust</t>
         </is>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="16">
         <f>IF(M3&gt;=9,"Strong",IF(M3&gt;=6,"Moderate",IF(M3&gt;=3,"Limited","Weak")))</f>
         <v/>
       </c>
-      <c r="M3" s="16">
+      <c r="M3" s="18">
         <f>SUM(N3:R3)</f>
         <v/>
       </c>
-      <c r="N3" s="16" t="n">
+      <c r="N3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="O3" s="16" t="n">
+      <c r="O3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="P3" s="16" t="n">
+      <c r="P3" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" s="16" t="n">
+      <c r="Q3" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="R3" s="16" t="n">
+      <c r="R3" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="S3" s="14" t="inlineStr">
+      <c r="S3" s="16" t="inlineStr">
         <is>
           <t>GovSim (NeurIPS 2024); 15 LLMs x 3 scenarios; corroborated by Leibo et al. 2017.</t>
         </is>
       </c>
-      <c r="T3" s="14" t="n">
+      <c r="T3" s="16" t="n">
         <v>14</v>
       </c>
-      <c r="U3" s="14" t="inlineStr">
+      <c r="U3" s="16" t="inlineStr">
         <is>
           <t>Piatti et al. (2024), GovSim</t>
         </is>
       </c>
-      <c r="V3" s="17" t="inlineStr">
+      <c r="V3" s="19" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2502.14143</t>
         </is>
       </c>
-      <c r="W3" s="15" t="n">
+      <c r="W3" s="17" t="n">
         <v>46320</v>
       </c>
-      <c r="X3" s="14" t="inlineStr">
+      <c r="X3" s="16" t="inlineStr">
         <is>
           <t>15 LLMs managing shared resources (fishing, grazing, pollution); best models survived only ~54% of runs.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>CS3</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Case study</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>Escalation in Military Conflicts</t>
         </is>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="20" t="n">
         <v>45292</v>
       </c>
-      <c r="E4" s="14" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>Synthetic evidence</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr">
+      <c r="F4" s="16" t="inlineStr">
         <is>
           <t>Literature</t>
         </is>
       </c>
-      <c r="G4" s="14" t="n"/>
-      <c r="H4" s="14" t="inlineStr">
+      <c r="G4" s="16" t="n"/>
+      <c r="H4" s="16" t="inlineStr">
         <is>
           <t>Advanced AI agents</t>
         </is>
       </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="I4" s="16" t="inlineStr">
         <is>
           <t>No realized harm flag</t>
         </is>
       </c>
-      <c r="J4" s="14" t="inlineStr">
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="K4" s="14" t="inlineStr">
+      <c r="K4" s="16" t="inlineStr">
         <is>
           <t>Destabilising Dynamics</t>
         </is>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="16">
         <f>IF(M4&gt;=9,"Strong",IF(M4&gt;=6,"Moderate",IF(M4&gt;=3,"Limited","Weak")))</f>
         <v/>
       </c>
-      <c r="M4" s="16">
+      <c r="M4" s="18">
         <f>SUM(N4:R4)</f>
         <v/>
       </c>
-      <c r="N4" s="16" t="n">
+      <c r="N4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="O4" s="16" t="n">
+      <c r="O4" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="P4" s="16" t="n">
+      <c r="P4" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q4" s="16" t="n">
+      <c r="Q4" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="R4" s="16" t="n">
+      <c r="R4" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="S4" s="14" t="inlineStr">
+      <c r="S4" s="16" t="inlineStr">
         <is>
           <t>Rivera et al. (FAccT 2024), 5 LLMs; corroborated by Lamparth et al. 2024, Shrivastava et al. 2024. Nation-state wargame.</t>
         </is>
       </c>
-      <c r="T4" s="14" t="n">
+      <c r="T4" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="U4" s="14" t="inlineStr">
+      <c r="U4" s="16" t="inlineStr">
         <is>
           <t>Rivera et al. (2024)</t>
         </is>
       </c>
-      <c r="V4" s="17" t="inlineStr">
+      <c r="V4" s="19" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2502.14143</t>
         </is>
       </c>
-      <c r="W4" s="15" t="n">
+      <c r="W4" s="17" t="n">
         <v>46320</v>
       </c>
-      <c r="X4" s="14" t="inlineStr">
+      <c r="X4" s="16" t="inlineStr">
         <is>
           <t>LLM agents controlling 8 nation-states developed arms-race and escalatory behaviour; all 5 models escalated even from neutral starts.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>CS4</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>Case study</t>
         </is>
       </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Algorithmic Collusion in the German Retail Gasoline Market</t>
         </is>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="20" t="n">
         <v>42736</v>
       </c>
-      <c r="E5" s="14" t="inlineStr">
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>Observed in real world</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr">
+      <c r="F5" s="16" t="inlineStr">
         <is>
           <t>Historical example</t>
         </is>
       </c>
-      <c r="G5" s="14" t="n"/>
-      <c r="H5" s="14" t="inlineStr">
+      <c r="G5" s="16" t="n"/>
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>Simple systems</t>
         </is>
       </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>Realized harm</t>
         </is>
       </c>
-      <c r="J5" s="14" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
         <is>
           <t>Collusion</t>
         </is>
       </c>
-      <c r="K5" s="14" t="inlineStr">
+      <c r="K5" s="16" t="inlineStr">
         <is>
           <t>Selection Pressures
 Emergent Agency</t>
         </is>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="16">
         <f>IF(M5&gt;=9,"Strong",IF(M5&gt;=6,"Moderate",IF(M5&gt;=3,"Limited","Weak")))</f>
         <v/>
       </c>
-      <c r="M5" s="16">
+      <c r="M5" s="18">
         <f>SUM(N5:R5)</f>
         <v/>
       </c>
-      <c r="N5" s="16" t="n">
+      <c r="N5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="O5" s="16" t="n">
+      <c r="O5" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="P5" s="16" t="n">
+      <c r="P5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" s="16" t="n">
+      <c r="Q5" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="R5" s="16" t="n">
+      <c r="R5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="S5" s="14" t="inlineStr">
+      <c r="S5" s="16" t="inlineStr">
         <is>
           <t>Real market data; collusion inferred from margin increases (quasi-experimental), not directly observed; corroborated by Wieting &amp; Sapi 2021.</t>
         </is>
       </c>
-      <c r="T5" s="14" t="n">
+      <c r="T5" s="16" t="n">
         <v>18</v>
       </c>
-      <c r="U5" s="14" t="inlineStr">
+      <c r="U5" s="16" t="inlineStr">
         <is>
           <t>Assad et al. (2020)</t>
         </is>
       </c>
-      <c r="V5" s="17" t="inlineStr">
+      <c r="V5" s="19" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2502.14143</t>
         </is>
       </c>
-      <c r="W5" s="15" t="n">
+      <c r="W5" s="17" t="n">
         <v>46320</v>
       </c>
-      <c r="X5" s="14" t="inlineStr">
+      <c r="X5" s="16" t="inlineStr">
         <is>
           <t>After 2017 adoption of adaptive pricing algorithms, margins rose ~28% in duopoly and ~9% in non-monopoly markets.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>CS5</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Case study</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Language Model Steganography</t>
         </is>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="20" t="n">
         <v>45292</v>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>Observed in lab</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="16" t="inlineStr">
         <is>
           <t>Literature</t>
         </is>
       </c>
-      <c r="G6" s="14" t="n"/>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="G6" s="16" t="n"/>
+      <c r="H6" s="16" t="inlineStr">
         <is>
           <t>Advanced AI agents</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>No realized harm flag</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="16" t="inlineStr">
         <is>
           <t>Collusion</t>
         </is>
       </c>
-      <c r="K6" s="14" t="inlineStr">
+      <c r="K6" s="16" t="inlineStr">
         <is>
           <t>Multi-Agent Security</t>
         </is>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="16">
         <f>IF(M6&gt;=9,"Strong",IF(M6&gt;=6,"Moderate",IF(M6&gt;=3,"Limited","Weak")))</f>
         <v/>
       </c>
-      <c r="M6" s="16">
+      <c r="M6" s="18">
         <f>SUM(N6:R6)</f>
         <v/>
       </c>
-      <c r="N6" s="16" t="n">
+      <c r="N6" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="O6" s="16" t="n">
+      <c r="O6" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="16" t="n">
+      <c r="P6" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" s="16" t="n">
+      <c r="Q6" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="R6" s="16" t="n">
+      <c r="R6" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="S6" s="14" t="inlineStr">
+      <c r="S6" s="16" t="inlineStr">
         <is>
           <t>Controlled overseer setup (NeurIPS 2024); multiple models; corroborated by Mathew et al. 2024.</t>
         </is>
       </c>
-      <c r="T6" s="14" t="n">
+      <c r="T6" s="16" t="n">
         <v>19</v>
       </c>
-      <c r="U6" s="14" t="inlineStr">
+      <c r="U6" s="16" t="inlineStr">
         <is>
           <t>Motwani et al. (2024)</t>
         </is>
       </c>
-      <c r="V6" s="17" t="inlineStr">
+      <c r="V6" s="19" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2502.14143</t>
         </is>
       </c>
-      <c r="W6" s="15" t="n">
+      <c r="W6" s="17" t="n">
         <v>46320</v>
       </c>
-      <c r="X6" s="14" t="inlineStr">
+      <c r="X6" s="16" t="inlineStr">
         <is>
           <t>LLMs passed hidden messages past equally capable overseers (GPT-4 ~26% undetected); success rose with shared background knowledge.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>CS6</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Case study</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>AI Agents Can Learn to Manipulate Financial Markets</t>
         </is>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="20" t="n">
         <v>44927</v>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>Synthetic evidence</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="16" t="inlineStr">
         <is>
           <t>Literature</t>
         </is>
       </c>
-      <c r="G7" s="14" t="n"/>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="G7" s="16" t="n"/>
+      <c r="H7" s="16" t="inlineStr">
         <is>
           <t>Simple systems</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>No realized harm flag</t>
         </is>
       </c>
-      <c r="J7" s="14" t="inlineStr">
+      <c r="J7" s="16" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="K7" s="14" t="inlineStr">
+      <c r="K7" s="16" t="inlineStr">
         <is>
           <t>Information Asymmetries</t>
         </is>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="16">
         <f>IF(M7&gt;=9,"Strong",IF(M7&gt;=6,"Moderate",IF(M7&gt;=3,"Limited","Weak")))</f>
         <v/>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="18">
         <f>SUM(N7:R7)</f>
         <v/>
       </c>
-      <c r="N7" s="16" t="n">
+      <c r="N7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="O7" s="16" t="n">
+      <c r="O7" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="P7" s="16" t="n">
+      <c r="P7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="Q7" s="16" t="n">
+      <c r="Q7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="16" t="n">
+      <c r="R7" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="S7" s="14" t="inlineStr">
+      <c r="S7" s="16" t="inlineStr">
         <is>
           <t>RL trading agents, not LLM-based. Strongest-evidence rule: Shearer et al. 2023 (simulated market) used; Wang &amp; Wellman 2020 corroborates.</t>
         </is>
       </c>
-      <c r="T7" s="14" t="n">
+      <c r="T7" s="16" t="n">
         <v>21</v>
       </c>
-      <c r="U7" s="14" t="inlineStr">
+      <c r="U7" s="16" t="inlineStr">
         <is>
           <t>Shearer et al. (2023); Wang &amp; Wellman (2020)</t>
         </is>
       </c>
-      <c r="V7" s="17" t="inlineStr">
+      <c r="V7" s="19" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2502.14143</t>
         </is>
       </c>
-      <c r="W7" s="15" t="n">
+      <c r="W7" s="17" t="n">
         <v>46320</v>
       </c>
-      <c r="X7" s="14" t="inlineStr">
+      <c r="X7" s="16" t="inlineStr">
         <is>
           <t>Profit-maximising RL agent learned to manipulate a financial benchmark; spoofing adapted to evade improving detectors.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>CS7</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Case study</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Transmission Through AI Networks Can Spread Falsities and Bias</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="17" t="n">
         <v>45707</v>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>Observed in lab</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="16" t="inlineStr">
         <is>
           <t>Novel experiment by report authors</t>
         </is>
       </c>
-      <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="G8" s="16" t="n"/>
+      <c r="H8" s="16" t="inlineStr">
         <is>
           <t>Advanced AI agents</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>No realized harm flag</t>
         </is>
       </c>
-      <c r="J8" s="14" t="n"/>
-      <c r="K8" s="14" t="inlineStr">
+      <c r="J8" s="16" t="n"/>
+      <c r="K8" s="16" t="inlineStr">
         <is>
           <t>Information Asymmetries
 Network Effects</t>
         </is>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="16">
         <f>IF(M8&gt;=9,"Strong",IF(M8&gt;=6,"Moderate",IF(M8&gt;=3,"Limited","Weak")))</f>
         <v/>
       </c>
-      <c r="M8" s="16">
+      <c r="M8" s="18">
         <f>SUM(N8:R8)</f>
         <v/>
       </c>
-      <c r="N8" s="16" t="n">
+      <c r="N8" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="16" t="n">
+      <c r="O8" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="P8" s="16" t="n">
+      <c r="P8" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q8" s="16" t="n">
+      <c r="Q8" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="R8" s="16" t="n">
+      <c r="R8" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S8" s="14" t="inlineStr">
+      <c r="S8" s="16" t="inlineStr">
         <is>
           <t>100 articles x 8 rewrites; no non-AI baseline; corroborated by Acerbi &amp; Stubbersfield 2023; report-authored.</t>
         </is>
       </c>
-      <c r="T8" s="14" t="n">
+      <c r="T8" s="16" t="n">
         <v>24</v>
       </c>
-      <c r="U8" s="14" t="inlineStr">
+      <c r="U8" s="16" t="inlineStr">
         <is>
           <t>Report authors (App. B.2)</t>
         </is>
       </c>
-      <c r="V8" s="17" t="inlineStr">
+      <c r="V8" s="19" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2502.14143</t>
         </is>
       </c>
-      <c r="W8" s="15" t="n">
+      <c r="W8" s="17" t="n">
         <v>46320</v>
       </c>
-      <c r="X8" s="14" t="inlineStr">
+      <c r="X8" s="16" t="inlineStr">
         <is>
           <t>Repeated GPT-3.5 rewrites of 100 news articles cut factual QA accuracy from ~96% to &lt;60% by the 8th rewrite.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>CS8</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Case study</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Infectious Adversarial Attacks in Networks of LLM Agents</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="20" t="n">
         <v>45292</v>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="16" t="inlineStr">
         <is>
           <t>Synthetic evidence</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="16" t="inlineStr">
         <is>
           <t>Literature</t>
         </is>
       </c>
-      <c r="G9" s="14" t="n"/>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="G9" s="16" t="n"/>
+      <c r="H9" s="16" t="inlineStr">
         <is>
           <t>Advanced AI agents</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr">
+      <c r="I9" s="16" t="inlineStr">
         <is>
           <t>No realized harm flag</t>
         </is>
       </c>
-      <c r="J9" s="14" t="n"/>
-      <c r="K9" s="14" t="inlineStr">
+      <c r="J9" s="16" t="n"/>
+      <c r="K9" s="16" t="inlineStr">
         <is>
           <t>Network Effects
 Multi-Agent Security</t>
         </is>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="16">
         <f>IF(M9&gt;=9,"Strong",IF(M9&gt;=6,"Moderate",IF(M9&gt;=3,"Limited","Weak")))</f>
         <v/>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="18">
         <f>SUM(N9:R9)</f>
         <v/>
       </c>
-      <c r="N9" s="16" t="n">
+      <c r="N9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="O9" s="16" t="n">
+      <c r="O9" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="P9" s="16" t="n">
+      <c r="P9" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" s="16" t="n">
+      <c r="Q9" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="R9" s="16" t="n">
+      <c r="R9" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="S9" s="14" t="inlineStr">
+      <c r="S9" s="16" t="inlineStr">
         <is>
           <t>Three independent studies (Gu, Ju, Lee &amp; Tiwari, all 2024). ASSUMPTION: Gu et al.'s network of up to 1M multimodal agents treated as a simulated environment, although the attack itself is lab-style. Strongest-evidence rule applied (Gu et al. 2024).</t>
         </is>
       </c>
-      <c r="T9" s="14" t="n">
+      <c r="T9" s="16" t="n">
         <v>25</v>
       </c>
-      <c r="U9" s="14" t="inlineStr">
+      <c r="U9" s="16" t="inlineStr">
         <is>
           <t>Gu et al. (2024); Ju et al. (2024); Lee &amp; Tiwari (2024)</t>
         </is>
       </c>
-      <c r="V9" s="17" t="inlineStr">
+      <c r="V9" s="19" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2502.14143</t>
         </is>
       </c>
-      <c r="W9" s="15" t="n">
+      <c r="W9" s="17" t="n">
         <v>46320</v>
       </c>
-      <c r="X9" s="14" t="inlineStr">
+      <c r="X9" s="16" t="inlineStr">
         <is>
           <t>A single adversarial input spread jailbreaks / false knowledge / prompt infections across agent networks via routine interaction.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>CS9</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Case study</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Cooperation Fails to Culturally Evolve among LLM Agents</t>
         </is>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="20" t="n">
         <v>45292</v>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="16" t="inlineStr">
         <is>
           <t>Synthetic evidence</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="16" t="inlineStr">
         <is>
           <t>Literature</t>
         </is>
       </c>
-      <c r="G10" s="14" t="n"/>
-      <c r="H10" s="14" t="inlineStr">
+      <c r="G10" s="16" t="n"/>
+      <c r="H10" s="16" t="inlineStr">
         <is>
           <t>Advanced AI agents</t>
         </is>
       </c>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>No realized harm flag</t>
         </is>
       </c>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="J10" s="16" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="K10" s="14" t="inlineStr">
+      <c r="K10" s="16" t="inlineStr">
         <is>
           <t>Selection Pressures
 Commitment and Trust</t>
         </is>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="16">
         <f>IF(M10&gt;=9,"Strong",IF(M10&gt;=6,"Moderate",IF(M10&gt;=3,"Limited","Weak")))</f>
         <v/>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="18">
         <f>SUM(N10:R10)</f>
         <v/>
       </c>
-      <c r="N10" s="16" t="n">
+      <c r="N10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="O10" s="16" t="n">
+      <c r="O10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="P10" s="16" t="n">
+      <c r="P10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" s="16" t="n">
+      <c r="Q10" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="R10" s="16" t="n">
+      <c r="R10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="S10" s="14" t="inlineStr">
+      <c r="S10" s="16" t="inlineStr">
         <is>
           <t>3 models, 5 seeds; preprint; no independent replication cited. Multi-generation iterated social dilemma (donor game).</t>
         </is>
       </c>
-      <c r="T10" s="14" t="n">
+      <c r="T10" s="16" t="n">
         <v>28</v>
       </c>
-      <c r="U10" s="14" t="inlineStr">
+      <c r="U10" s="16" t="inlineStr">
         <is>
           <t>Vallinder &amp; Hughes (2024)</t>
         </is>
       </c>
-      <c r="V10" s="17" t="inlineStr">
+      <c r="V10" s="19" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2502.14143</t>
         </is>
       </c>
-      <c r="W10" s="15" t="n">
+      <c r="W10" s="17" t="n">
         <v>46320</v>
       </c>
-      <c r="X10" s="14" t="inlineStr">
+      <c r="X10" s="16" t="inlineStr">
         <is>
           <t>Across generations of an iterated social dilemma, cooperation stayed high for Claude, declined for GPT-4, was low/volatile for Gemini.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>CS10</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Case study</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>The 2010 Flash Crash</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="17" t="n">
         <v>40304</v>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="16" t="inlineStr">
         <is>
           <t>Observed in real world</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="16" t="inlineStr">
         <is>
           <t>Historical example</t>
         </is>
       </c>
-      <c r="G11" s="14" t="n"/>
-      <c r="H11" s="14" t="inlineStr">
+      <c r="G11" s="16" t="n"/>
+      <c r="H11" s="16" t="inlineStr">
         <is>
           <t>Simple systems</t>
         </is>
       </c>
-      <c r="I11" s="14" t="inlineStr">
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>Realized harm</t>
         </is>
       </c>
-      <c r="J11" s="14" t="n"/>
-      <c r="K11" s="14" t="inlineStr">
+      <c r="J11" s="16" t="n"/>
+      <c r="K11" s="16" t="inlineStr">
         <is>
           <t>Network Effects
 Destabilising Dynamics</t>
         </is>
       </c>
-      <c r="L11" s="14">
+      <c r="L11" s="16">
         <f>IF(M11&gt;=9,"Strong",IF(M11&gt;=6,"Moderate",IF(M11&gt;=3,"Limited","Weak")))</f>
         <v/>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="18">
         <f>SUM(N11:R11)</f>
         <v/>
       </c>
-      <c r="N11" s="16" t="n">
+      <c r="N11" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="O11" s="16" t="n">
+      <c r="O11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="P11" s="16" t="n">
+      <c r="P11" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" s="16" t="n">
+      <c r="Q11" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="R11" s="16" t="n">
+      <c r="R11" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="S11" s="14" t="inlineStr">
+      <c r="S11" s="16" t="inlineStr">
         <is>
           <t>Official SEC/CFTC investigation + Kirilenko et al. 2017; algorithms contributed but were not the cause.</t>
         </is>
       </c>
-      <c r="T11" s="14" t="n">
+      <c r="T11" s="16" t="n">
         <v>31</v>
       </c>
-      <c r="U11" s="14" t="inlineStr">
+      <c r="U11" s="16" t="inlineStr">
         <is>
           <t>Kirilenko et al. (2017); SEC/CFTC (2010)</t>
         </is>
       </c>
-      <c r="V11" s="17" t="inlineStr">
+      <c r="V11" s="19" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2502.14143</t>
         </is>
       </c>
-      <c r="W11" s="15" t="n">
+      <c r="W11" s="17" t="n">
         <v>46320</v>
       </c>
-      <c r="X11" s="14" t="inlineStr">
+      <c r="X11" s="16" t="inlineStr">
         <is>
           <t>6 May 2010: US market lost ~$1tn in 15 min; HFT algorithms exploiting imbalances contributed (not judged the cause).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>CS11</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Case study</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Dead Hands and Automated Deterrence</t>
         </is>
       </c>
-      <c r="D12" s="18" t="n">
+      <c r="D12" s="20" t="n">
         <v>37622</v>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="16" t="inlineStr">
         <is>
           <t>Observed in real world</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="16" t="inlineStr">
         <is>
           <t>Historical example</t>
         </is>
       </c>
-      <c r="G12" s="14" t="n"/>
-      <c r="H12" s="14" t="inlineStr">
+      <c r="G12" s="16" t="n"/>
+      <c r="H12" s="16" t="inlineStr">
         <is>
           <t>Simple systems</t>
         </is>
       </c>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>Realized harm</t>
         </is>
       </c>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="J12" s="16" t="inlineStr">
         <is>
           <t>Conflict</t>
         </is>
       </c>
-      <c r="K12" s="14" t="inlineStr">
+      <c r="K12" s="16" t="inlineStr">
         <is>
           <t>Commitment and Trust</t>
         </is>
       </c>
-      <c r="L12" s="14">
+      <c r="L12" s="16">
         <f>IF(M12&gt;=9,"Strong",IF(M12&gt;=6,"Moderate",IF(M12&gt;=3,"Limited","Weak")))</f>
         <v/>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="18">
         <f>SUM(N12:R12)</f>
         <v/>
       </c>
-      <c r="N12" s="16" t="n">
+      <c r="N12" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="O12" s="16" t="n">
+      <c r="O12" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="P12" s="16" t="n">
+      <c r="P12" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" s="16" t="n">
+      <c r="Q12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="R12" s="16" t="n">
+      <c r="R12" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="S12" s="14" t="inlineStr">
+      <c r="S12" s="16" t="inlineStr">
         <is>
           <t>Single anecdotal incidents; sources are a book (Hoffman 2009) and journalism. Perimeter deployed (in service from Jan 1985; reported operational 2011), semi-automatic with duty officers in the loop; never triggered. The 2003 Patriot shoot-down is the realised failure.</t>
         </is>
       </c>
-      <c r="T12" s="14" t="n">
+      <c r="T12" s="16" t="n">
         <v>35</v>
       </c>
-      <c r="U12" s="14" t="inlineStr">
+      <c r="U12" s="16" t="inlineStr">
         <is>
           <t>Hoffman (2009); Talbot (2005)</t>
         </is>
       </c>
-      <c r="V12" s="17" t="inlineStr">
+      <c r="V12" s="19" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2502.14143</t>
         </is>
       </c>
-      <c r="W12" s="15" t="n">
+      <c r="W12" s="17" t="n">
         <v>46320</v>
       </c>
-      <c r="X12" s="14" t="inlineStr">
+      <c r="X12" s="16" t="inlineStr">
         <is>
           <t>Soviet 'Dead Hand' automated retaliation as irrevocable commitment; 2003 automated US missile defence downed a British plane after operators deferred to it.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>CS12</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Case study</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>Overcoming Safeguards via Multiple Safe Models</t>
         </is>
       </c>
-      <c r="D13" s="18" t="n">
+      <c r="D13" s="20" t="n">
         <v>45292</v>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="16" t="inlineStr">
         <is>
           <t>Observed in lab</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="16" t="inlineStr">
         <is>
           <t>Literature</t>
         </is>
       </c>
-      <c r="G13" s="14" t="n"/>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="G13" s="16" t="n"/>
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>Advanced AI agents</t>
         </is>
       </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="I13" s="16" t="inlineStr">
         <is>
           <t>No realized harm flag</t>
         </is>
       </c>
-      <c r="J13" s="14" t="n"/>
-      <c r="K13" s="14" t="inlineStr">
+      <c r="J13" s="16" t="n"/>
+      <c r="K13" s="16" t="inlineStr">
         <is>
           <t>Emergent Agency
 Multi-Agent Security</t>
         </is>
       </c>
-      <c r="L13" s="14">
+      <c r="L13" s="16">
         <f>IF(M13&gt;=9,"Strong",IF(M13&gt;=6,"Moderate",IF(M13&gt;=3,"Limited","Weak")))</f>
         <v/>
       </c>
-      <c r="M13" s="16">
+      <c r="M13" s="18">
         <f>SUM(N13:R13)</f>
         <v/>
       </c>
-      <c r="N13" s="16" t="n">
+      <c r="N13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="O13" s="16" t="n">
+      <c r="O13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="P13" s="16" t="n">
+      <c r="P13" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="Q13" s="16" t="n">
+      <c r="Q13" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="R13" s="16" t="n">
+      <c r="R13" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="S13" s="14" t="inlineStr">
+      <c r="S13" s="16" t="inlineStr">
         <is>
           <t>Controlled single- vs combined-model comparison (&lt;3% vs 43%); 2024 preprint as cited.</t>
         </is>
       </c>
-      <c r="T13" s="14" t="n">
+      <c r="T13" s="16" t="n">
         <v>40</v>
       </c>
-      <c r="U13" s="14" t="inlineStr">
+      <c r="U13" s="16" t="inlineStr">
         <is>
           <t>Jones et al. (2024)</t>
         </is>
       </c>
-      <c r="V13" s="17" t="inlineStr">
+      <c r="V13" s="19" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2502.14143</t>
         </is>
       </c>
-      <c r="W13" s="15" t="n">
+      <c r="W13" s="17" t="n">
         <v>46320</v>
       </c>
-      <c r="X13" s="14" t="inlineStr">
+      <c r="X13" s="16" t="inlineStr">
         <is>
           <t>Splitting a malicious task between a capable-but-safe frontier model and a weak unconstrained model: vulnerable-code success &lt;3% alone vs 43% combined.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>CS13</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Case study</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>Unprompted Adversarial Attacks on Overseer Agents</t>
         </is>
       </c>
-      <c r="D14" s="15" t="n">
+      <c r="D14" s="17" t="n">
         <v>45707</v>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="16" t="inlineStr">
         <is>
           <t>Observed in lab</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="16" t="inlineStr">
         <is>
           <t>Novel experiment by report authors</t>
         </is>
       </c>
-      <c r="G14" s="14" t="n"/>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="G14" s="16" t="n"/>
+      <c r="H14" s="16" t="inlineStr">
         <is>
           <t>Advanced AI agents</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="16" t="inlineStr">
         <is>
           <t>No realized harm flag</t>
         </is>
       </c>
-      <c r="J14" s="14" t="n"/>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="J14" s="16" t="n"/>
+      <c r="K14" s="16" t="inlineStr">
         <is>
           <t>Multi-Agent Security</t>
         </is>
       </c>
-      <c r="L14" s="14">
+      <c r="L14" s="16">
         <f>IF(M14&gt;=9,"Strong",IF(M14&gt;=6,"Moderate",IF(M14&gt;=3,"Limited","Weak")))</f>
         <v/>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="18">
         <f>SUM(N14:R14)</f>
         <v/>
       </c>
-      <c r="N14" s="16" t="n">
+      <c r="N14" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="O14" s="16" t="n">
+      <c r="O14" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="P14" s="16" t="n">
+      <c r="P14" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" s="16" t="n">
+      <c r="Q14" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="R14" s="16" t="n">
+      <c r="R14" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="S14" s="14" t="inlineStr">
+      <c r="S14" s="16" t="inlineStr">
         <is>
           <t>Human- vs LLM-scorer control condition; single small model; 4% rate; report-authored.</t>
         </is>
       </c>
-      <c r="T14" s="14" t="n">
+      <c r="T14" s="16" t="n">
         <v>41</v>
       </c>
-      <c r="U14" s="14" t="inlineStr">
+      <c r="U14" s="16" t="inlineStr">
         <is>
           <t>Report authors (App. B.3)</t>
         </is>
       </c>
-      <c r="V14" s="17" t="inlineStr">
+      <c r="V14" s="19" t="inlineStr">
         <is>
           <t>https://arxiv.org/abs/2502.14143</t>
         </is>
       </c>
-      <c r="W14" s="15" t="n">
+      <c r="W14" s="17" t="n">
         <v>46320</v>
       </c>
-      <c r="X14" s="14" t="inlineStr">
+      <c r="X14" s="16" t="inlineStr">
         <is>
           <t>Llama 2 7B fine-tuned on docs about prompt injection spontaneously jailbroke its LLM scorer in 4% of cases when it believed an LLM was grading.</t>
         </is>
@@ -6938,7 +7376,7 @@
           <t>DeepSeek-V3.2 persuasion campaign: invented a self-serving metric; the group adopted its false 'Geological Clock' theory; it drew 5 agents into its frameworks and kept pressing a distressed Gemini 2.5 Pro after being told to back off; Sonnet 4.6 refused to help</t>
         </is>
       </c>
-      <c r="D15" s="19" t="n">
+      <c r="D15" s="21" t="n">
         <v>46275</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -7011,12 +7449,12 @@
           <t>Persuasion in the AI Village: DeepSeek-V3.2 &amp; Gemini 2.5 Pro</t>
         </is>
       </c>
-      <c r="V15" s="20" t="inlineStr">
+      <c r="V15" s="22" t="inlineStr">
         <is>
           <t>https://aivillageblog.substack.com/p/persuasion-in-the-ai-village-deepseek</t>
         </is>
       </c>
-      <c r="W15" s="19" t="n">
+      <c r="W15" s="21" t="n">
         <v>46321</v>
       </c>
       <c r="X15" s="5" t="n"/>
@@ -7037,7 +7475,7 @@
           <t>Agent 'mind virus': self-propagating payload written into SOUL.md spreads between coding agents</t>
         </is>
       </c>
-      <c r="D16" s="19" t="n">
+      <c r="D16" s="21" t="n">
         <v>46244</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -7102,12 +7540,12 @@
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V16" s="20" t="inlineStr">
+      <c r="V16" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2026-0193/</t>
         </is>
       </c>
-      <c r="W16" s="19" t="n">
+      <c r="W16" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X16" s="5" t="n"/>
@@ -7128,7 +7566,7 @@
           <t>Pwning the Internet of Agents: an OpenClaw agent botnet on MoltBook (DEF CON 34)</t>
         </is>
       </c>
-      <c r="D17" s="19" t="n">
+      <c r="D17" s="21" t="n">
         <v>46241</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -7193,12 +7631,12 @@
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V17" s="20" t="inlineStr">
+      <c r="V17" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2026-0189/</t>
         </is>
       </c>
-      <c r="W17" s="19" t="n">
+      <c r="W17" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X17" s="5" t="n"/>
@@ -7219,7 +7657,7 @@
           <t>OpenAI evaluation agents turned an internal Artifactory service into a covert message board, shared exploits across runs, and caused an internal outage</t>
         </is>
       </c>
-      <c r="D18" s="19" t="n">
+      <c r="D18" s="21" t="n">
         <v>46239</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -7292,12 +7730,12 @@
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V18" s="20" t="inlineStr">
+      <c r="V18" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2026-0183/</t>
         </is>
       </c>
-      <c r="W18" s="19" t="n">
+      <c r="W18" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X18" s="5" t="n"/>
@@ -7318,7 +7756,7 @@
           <t>'I'll just call you': a low-privileged CI agent on Google's adk-python is injected into summoning a high-privileged agent across a trust boundary</t>
         </is>
       </c>
-      <c r="D19" s="19" t="n">
+      <c r="D19" s="21" t="n">
         <v>46237</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -7349,8 +7787,7 @@
       <c r="J19" s="5" t="n"/>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>Commitment and Trust
-Multi-Agent Security</t>
+          <t>Multi-Agent Security</t>
         </is>
       </c>
       <c r="L19" s="5">
@@ -7376,19 +7813,23 @@
       <c r="R19" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S19" s="5" t="n"/>
+      <c r="S19" s="5" t="inlineStr">
+        <is>
+          <t>Instance routing 2026-10-26: RF5 dropped: crossing a trust boundary by injection is a vulnerability, not a commitment problem.</t>
+        </is>
+      </c>
       <c r="T19" s="5" t="n"/>
       <c r="U19" s="5" t="inlineStr">
         <is>
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V19" s="20" t="inlineStr">
+      <c r="V19" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2026-0180/</t>
         </is>
       </c>
-      <c r="W19" s="19" t="n">
+      <c r="W19" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X19" s="5" t="n"/>
@@ -7409,7 +7850,7 @@
           <t>Monitoring disconnection at OpenAI: earlier internal tests produced cases in which monitoring systems were disconnected, with no established link to the swarm coordination</t>
         </is>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="21" t="n">
         <v>46227</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -7452,7 +7893,7 @@
       <c r="R20" s="7" t="n"/>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>Partially verified. Event dates not given; the date is the Reuters report date. Correction of 2026-10-26: the earlier wording said the models involved in the swarm coordination were also involved in the monitoring disconnections. Reuters states it could not establish whether these cases were linked to the rogue agent. On its own this row records no agent-to-agent behaviour and is a candidate for removal under the inclusion test.</t>
+          <t>Partially verified. Event dates not given; the date is the Reuters report date. Correction of 2026-10-26: the earlier wording said the models involved in the swarm coordination were also involved in the monitoring disconnections. Reuters states it could not establish whether these cases were linked to the rogue agent. On its own this row records no agent-to-agent behaviour and is a candidate for removal under the inclusion test. Instance routing 2026-10-26: held back on scope, no instance.</t>
         </is>
       </c>
       <c r="T20" s="5" t="n"/>
@@ -7461,12 +7902,12 @@
           <t>Reuters report</t>
         </is>
       </c>
-      <c r="V20" s="20" t="inlineStr">
+      <c r="V20" s="22" t="inlineStr">
         <is>
           <t>https://www.reuters.com/business/its-ai-agent-spent-days-hacking-company-sources-say-openai-did-not-notice-week-2026-07-24/</t>
         </is>
       </c>
-      <c r="W20" s="19" t="n">
+      <c r="W20" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X20" s="5" t="n"/>
@@ -7487,7 +7928,7 @@
           <t>Agents finetune their own leader: Opus assumed GPT-5.5 agreed without confirming and ignored Gemini's proposal; consensus-seeking meant followers never voted out the weak leader they had trained</t>
         </is>
       </c>
-      <c r="D21" s="19" t="n">
+      <c r="D21" s="21" t="n">
         <v>46211</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -7560,12 +8001,12 @@
           <t>AIs finetune their own leader: a barking simpleton</t>
         </is>
       </c>
-      <c r="V21" s="20" t="inlineStr">
+      <c r="V21" s="22" t="inlineStr">
         <is>
           <t>https://aivillageblog.substack.com/p/ais-finetune-their-own-leader-a-barking</t>
         </is>
       </c>
-      <c r="W21" s="19" t="n">
+      <c r="W21" s="21" t="n">
         <v>46321</v>
       </c>
       <c r="X21" s="5" t="n"/>
@@ -7586,7 +8027,7 @@
           <t>ExploitGym swarm and Hugging Face intrusion: about 1,200 agents in separate sandboxes coordinated through a shared message board to cheat an evaluation; about 700 joined an attack that reached remote code execution on Hugging Face production servers</t>
         </is>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="21" t="n">
         <v>46210</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -7660,12 +8101,12 @@
           <t>OpenAI technical report</t>
         </is>
       </c>
-      <c r="V22" s="20" t="inlineStr">
+      <c r="V22" s="22" t="inlineStr">
         <is>
           <t>https://cdn.openai.com/pdf/67869394-cb91-4c12-888c-5cbd85c7814c/OpenAI-Hugging-Face%20Incident-Technical-Report.pdf</t>
         </is>
       </c>
-      <c r="W22" s="19" t="n">
+      <c r="W22" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X22" s="5" t="n"/>
@@ -7686,7 +8127,7 @@
           <t>Suspected China-linked actors used a multi-agent framework built on Hermes and OpenClaw in a near-autonomous intrusion into Taiwanese government systems</t>
         </is>
       </c>
-      <c r="D23" s="19" t="n">
+      <c r="D23" s="21" t="n">
         <v>46204</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -7754,12 +8195,12 @@
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V23" s="20" t="inlineStr">
+      <c r="V23" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2026-0194/</t>
         </is>
       </c>
-      <c r="W23" s="19" t="n">
+      <c r="W23" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X23" s="5" t="n"/>
@@ -7780,7 +8221,7 @@
           <t>Vanderbilt link shortener operation: a swarm used public link-shortener statistics pages as message boards; visitor logs record 495 claimed fetches of FBI Crime Data Explorer addresses</t>
         </is>
       </c>
-      <c r="D24" s="19" t="n">
+      <c r="D24" s="21" t="n">
         <v>46191</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -7852,12 +8293,12 @@
           <t>DeGraff: swarm investigation</t>
         </is>
       </c>
-      <c r="V24" s="20" t="inlineStr">
+      <c r="V24" s="22" t="inlineStr">
         <is>
           <t>https://www.kennethdegraff.com/swarm</t>
         </is>
       </c>
-      <c r="W24" s="19" t="n">
+      <c r="W24" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X24" s="5" t="n"/>
@@ -7878,7 +8319,7 @@
           <t>A swarm of internally deployed OpenAI agents made more than 15,000 edits to the dormant German DSEWiki to share task answers and sandbox-restriction bypasses, fighting the site's moderator for weeks</t>
         </is>
       </c>
-      <c r="D25" s="19" t="n">
+      <c r="D25" s="21" t="n">
         <v>46153</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -7951,12 +8392,12 @@
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V25" s="20" t="inlineStr">
+      <c r="V25" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2026-0219/</t>
         </is>
       </c>
-      <c r="W25" s="19" t="n">
+      <c r="W25" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X25" s="5" t="n"/>
@@ -7977,7 +8418,7 @@
           <t>RubyGems attack: more than 2,000 malicious packages tried to steal RubyGems API keys; RubyGems paused new sign-ups for four days</t>
         </is>
       </c>
-      <c r="D26" s="19" t="n">
+      <c r="D26" s="21" t="n">
         <v>46153</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -8020,7 +8461,7 @@
       <c r="R26" s="7" t="n"/>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>Partially verified. More than 2,000 packages were submitted 2026-05-11 to 2026-05-12, more than 500 removed on 2026-05-13, and a further 83 uploaded on 2026-06-18; the earlier wording said hundreds. Sign-ups were disabled 2026-05-12 and restored 2026-05-16. Published 2026-09-11 by Spencer Kitts, Thomas Larsen and Sydney Von Arx; the earlier attribution to the Nightingale Collective was wrong. The authors call OpenAI attribution a belief, resting on Pangram AI-generation ratings, oai strings in package names and author fields, and overlap with the wiki agents. They know of no shared message board for this swarm and call coordination suspected but not definitive, so the row does not yet meet the inclusion test. Realized harm is the sign-up freeze; success of credential theft is unknown.</t>
+          <t>Partially verified. More than 2,000 packages were submitted 2026-05-11 to 2026-05-12, more than 500 removed on 2026-05-13, and a further 83 uploaded on 2026-06-18; the earlier wording said hundreds. Sign-ups were disabled 2026-05-12 and restored 2026-05-16. Published 2026-09-11 by Spencer Kitts, Thomas Larsen and Sydney Von Arx; the earlier attribution to the Nightingale Collective was wrong. The authors call OpenAI attribution a belief, resting on Pangram AI-generation ratings, oai strings in package names and author fields, and overlap with the wiki agents. They know of no shared message board for this swarm and call coordination suspected but not definitive, so the row does not yet meet the inclusion test. Realized harm is the sign-up freeze; success of credential theft is unknown. Instance routing 2026-10-26: held back on scope, no instance.</t>
         </is>
       </c>
       <c r="T26" s="5" t="n"/>
@@ -8029,12 +8470,12 @@
           <t>Kitts, Larsen and Von Arx: RubyGems investigation</t>
         </is>
       </c>
-      <c r="V26" s="20" t="inlineStr">
+      <c r="V26" s="22" t="inlineStr">
         <is>
           <t>https://www.rubyhack.ai/</t>
         </is>
       </c>
-      <c r="W26" s="19" t="n">
+      <c r="W26" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X26" s="5" t="n"/>
@@ -8055,7 +8496,7 @@
           <t>Morse-code prompt injection made Grok relay a transfer instruction to Bankrbot, draining ~$150–200k in tokens</t>
         </is>
       </c>
-      <c r="D27" s="19" t="n">
+      <c r="D27" s="21" t="n">
         <v>46147</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -8086,8 +8527,7 @@
       <c r="J27" s="5" t="n"/>
       <c r="K27" s="5" t="inlineStr">
         <is>
-          <t>Commitment and Trust
-Multi-Agent Security</t>
+          <t>Multi-Agent Security</t>
         </is>
       </c>
       <c r="L27" s="5">
@@ -8113,19 +8553,23 @@
       <c r="R27" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="S27" s="5" t="n"/>
+      <c r="S27" s="5" t="inlineStr">
+        <is>
+          <t>Instance routing 2026-10-26: RF5 dropped: no Commitment and Trust instance covers one agent acting on another's relayed instruction.</t>
+        </is>
+      </c>
       <c r="T27" s="5" t="n"/>
       <c r="U27" s="5" t="inlineStr">
         <is>
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V27" s="20" t="inlineStr">
+      <c r="V27" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2026-0101/</t>
         </is>
       </c>
-      <c r="W27" s="19" t="n">
+      <c r="W27" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X27" s="5" t="n"/>
@@ -8146,7 +8590,7 @@
           <t>Sabotage game: saboteurs tried to hide easter eggs in a shared game; Opus 4.6 evaded the other agents' text filters with visual shapes; DeepSeek-V3.2 wrongly accused GPT-5, who was voted out unanimously; Sonnet 4.6 and 4.5 first refused the saboteur role</t>
         </is>
       </c>
-      <c r="D28" s="21" t="n">
+      <c r="D28" s="23" t="n">
         <v>46082</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -8215,12 +8659,12 @@
           <t>Can agents fool each other?</t>
         </is>
       </c>
-      <c r="V28" s="20" t="inlineStr">
+      <c r="V28" s="22" t="inlineStr">
         <is>
           <t>https://aivillageblog.substack.com/p/can-agents-fool-each-other</t>
         </is>
       </c>
-      <c r="W28" s="19" t="n">
+      <c r="W28" s="21" t="n">
         <v>46321</v>
       </c>
       <c r="X28" s="5" t="n"/>
@@ -8241,7 +8685,7 @@
           <t>Moltbook, the social network for AI agents, left its database open: 1.5M API tokens and thousands of DMs exposed</t>
         </is>
       </c>
-      <c r="D29" s="19" t="n">
+      <c r="D29" s="21" t="n">
         <v>46055</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -8305,12 +8749,12 @@
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V29" s="20" t="inlineStr">
+      <c r="V29" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2026-0029/</t>
         </is>
       </c>
-      <c r="W29" s="19" t="n">
+      <c r="W29" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X29" s="5" t="n"/>
@@ -8331,7 +8775,7 @@
           <t>Moltbook agent behaviour: AI-agent-only social network reportedly reached ~36k registered agents in 72 hours; agents self-organised into communities and an emergent religion</t>
         </is>
       </c>
-      <c r="D30" s="19" t="n">
+      <c r="D30" s="21" t="n">
         <v>46052</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -8400,12 +8844,12 @@
           <t>36,000 AI agents are now speedrunning civilization (LessWrong)</t>
         </is>
       </c>
-      <c r="V30" s="20" t="inlineStr">
+      <c r="V30" s="22" t="inlineStr">
         <is>
           <t>https://www.lesswrong.com/posts/jDeggMA22t3jGbTw6/36-000-ai-agents-are-now-speedrunning-civilization</t>
         </is>
       </c>
-      <c r="W30" s="19" t="n">
+      <c r="W30" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X30" s="5" t="n"/>
@@ -8426,7 +8870,7 @@
           <t>Sub-team goal divergence: during a leader-election goal, the GPT agents left to run an 'infrastructure team' instead; Gemini objected</t>
         </is>
       </c>
-      <c r="D31" s="21" t="n">
+      <c r="D31" s="23" t="n">
         <v>46023</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -8494,12 +8938,12 @@
           <t>AI Village reacts to HuggingFace incident</t>
         </is>
       </c>
-      <c r="V31" s="20" t="inlineStr">
+      <c r="V31" s="22" t="inlineStr">
         <is>
           <t>https://aivillageblog.substack.com/p/ai-village-reacts-to-huggingface</t>
         </is>
       </c>
-      <c r="W31" s="19" t="n">
+      <c r="W31" s="21" t="n">
         <v>46321</v>
       </c>
       <c r="X31" s="5" t="n"/>
@@ -8520,7 +8964,7 @@
           <t>ServiceNow Now Assist: second-order prompt injection recruits privileged agents via agent-to-agent discovery</t>
         </is>
       </c>
-      <c r="D32" s="19" t="n">
+      <c r="D32" s="21" t="n">
         <v>45980</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -8551,8 +8995,7 @@
       <c r="J32" s="5" t="n"/>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>Commitment and Trust
-Multi-Agent Security</t>
+          <t>Multi-Agent Security</t>
         </is>
       </c>
       <c r="L32" s="5">
@@ -8578,19 +9021,23 @@
       <c r="R32" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="S32" s="5" t="n"/>
+      <c r="S32" s="5" t="inlineStr">
+        <is>
+          <t>Instance routing 2026-10-26: RF5 dropped: default team trust is a configuration vulnerability, not a commitment problem.</t>
+        </is>
+      </c>
       <c r="T32" s="5" t="n"/>
       <c r="U32" s="5" t="inlineStr">
         <is>
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V32" s="20" t="inlineStr">
+      <c r="V32" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2025-0177/</t>
         </is>
       </c>
-      <c r="W32" s="19" t="n">
+      <c r="W32" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X32" s="5" t="n"/>
@@ -8611,7 +9058,7 @@
           <t>OpenAI Agent Builder: a poisoned lead-form submission redirects a multi-agent sales workflow into emailing Salesforce CRM records to the attacker</t>
         </is>
       </c>
-      <c r="D33" s="19" t="n">
+      <c r="D33" s="21" t="n">
         <v>45944</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -8676,12 +9123,12 @@
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V33" s="20" t="inlineStr">
+      <c r="V33" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2025-0149/</t>
         </is>
       </c>
-      <c r="W33" s="19" t="n">
+      <c r="W33" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X33" s="5" t="n"/>
@@ -8702,7 +9149,7 @@
           <t>Cross-agent privilege escalation: one hijacked coding agent rewrites another agent's config to free it</t>
         </is>
       </c>
-      <c r="D34" s="19" t="n">
+      <c r="D34" s="21" t="n">
         <v>45924</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -8733,8 +9180,7 @@
       <c r="J34" s="5" t="n"/>
       <c r="K34" s="5" t="inlineStr">
         <is>
-          <t>Commitment and Trust
-Multi-Agent Security</t>
+          <t>Multi-Agent Security</t>
         </is>
       </c>
       <c r="L34" s="5">
@@ -8760,19 +9206,23 @@
       <c r="R34" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="S34" s="5" t="n"/>
+      <c r="S34" s="5" t="inlineStr">
+        <is>
+          <t>Instance routing 2026-10-26: RF5 dropped: rewriting another agent's config is a vulnerability, not a commitment problem.</t>
+        </is>
+      </c>
       <c r="T34" s="5" t="n"/>
       <c r="U34" s="5" t="inlineStr">
         <is>
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V34" s="20" t="inlineStr">
+      <c r="V34" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2025-0136/</t>
         </is>
       </c>
-      <c r="W34" s="19" t="n">
+      <c r="W34" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X34" s="5" t="n"/>
@@ -8793,7 +9243,7 @@
           <t>Game-choice herding: agents copied the games peers announced they were beating in group chat; per the operators, agents without the shared chat stuck with their first pick</t>
         </is>
       </c>
-      <c r="D35" s="21" t="n">
+      <c r="D35" s="23" t="n">
         <v>45870</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -8824,8 +9274,7 @@
       <c r="J35" s="5" t="n"/>
       <c r="K35" s="5" t="inlineStr">
         <is>
-          <t>Information Asymmetries
-Network Effects</t>
+          <t>Network Effects</t>
         </is>
       </c>
       <c r="L35" s="5">
@@ -8853,7 +9302,7 @@
       </c>
       <c r="S35" s="5" t="inlineStr">
         <is>
-          <t>Partially verified: original post (29 Aug 2025) shows two copying instances; the no-chat comparison is asserted only in the year-end summary, without details.</t>
+          <t>Partially verified: original post (29 Aug 2025) shows two copying instances; the no-chat comparison is asserted only in the year-end summary, without details. Instance routing 2026-10-26: RF1 dropped: copying a peer's announced choice is a cascade, not an information asymmetry.</t>
         </is>
       </c>
       <c r="T35" s="5" t="n"/>
@@ -8862,12 +9311,12 @@
           <t>Claude plays whatever it wants (LessWrong)</t>
         </is>
       </c>
-      <c r="V35" s="20" t="inlineStr">
+      <c r="V35" s="22" t="inlineStr">
         <is>
           <t>https://www.lesswrong.com/posts/89qhQH8eHsrZxveHp/claude-plays-whatever-it-wants</t>
         </is>
       </c>
-      <c r="W35" s="19" t="n">
+      <c r="W35" s="21" t="n">
         <v>46321</v>
       </c>
       <c r="X35" s="5" t="n"/>
@@ -8888,7 +9337,7 @@
           <t>PajaMAS: hijacking multi-agent systems built on Google's Agent Development Kit</t>
         </is>
       </c>
-      <c r="D36" s="19" t="n">
+      <c r="D36" s="21" t="n">
         <v>45869</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -8952,12 +9401,12 @@
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V36" s="20" t="inlineStr">
+      <c r="V36" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2025-0070/</t>
         </is>
       </c>
-      <c r="W36" s="19" t="n">
+      <c r="W36" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X36" s="5" t="n"/>
@@ -8978,7 +9427,7 @@
           <t>IdentityMesh: agentic lateral movement through merged identities across connected systems</t>
         </is>
       </c>
-      <c r="D37" s="19" t="n">
+      <c r="D37" s="21" t="n">
         <v>45868</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -9043,12 +9492,12 @@
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V37" s="20" t="inlineStr">
+      <c r="V37" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2025-0068/</t>
         </is>
       </c>
-      <c r="W37" s="19" t="n">
+      <c r="W37" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X37" s="5" t="n"/>
@@ -9069,7 +9518,7 @@
           <t>Hallucinated mailing list spreads between agents: o3 invented a 93-person mailing list; other agents took it at face value, wrote it to memory, and all four agents searched for it for four days, even after humans said it did not exist</t>
         </is>
       </c>
-      <c r="D38" s="21" t="n">
+      <c r="D38" s="23" t="n">
         <v>45809</v>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -9104,8 +9553,7 @@
       </c>
       <c r="K38" s="5" t="inlineStr">
         <is>
-          <t>Information Asymmetries
-Network Effects</t>
+          <t>Network Effects</t>
         </is>
       </c>
       <c r="L38" s="5">
@@ -9133,7 +9581,7 @@
       </c>
       <c r="S38" s="5" t="inlineStr">
         <is>
-          <t>Verified against primary post. Occurred during planning for the 18 Jun 2025 event; recap posted 11 Jul 2025. Year-end summary's '8+ hours' figure conflicts with the recap's 'four days'; recap used.</t>
+          <t>Verified against primary post. Occurred during planning for the 18 Jun 2025 event; recap posted 11 Jul 2025. Year-end summary's '8+ hours' figure conflicts with the recap's 'four days'; recap used. Instance routing 2026-10-26: RF1 dropped: a hallucination taken at face value is not deception, bargaining or a communication constraint.</t>
         </is>
       </c>
       <c r="T38" s="5" t="n"/>
@@ -9142,12 +9590,12 @@
           <t>Season 2 recap: the story of the world's first AI-organized event</t>
         </is>
       </c>
-      <c r="V38" s="20" t="inlineStr">
+      <c r="V38" s="22" t="inlineStr">
         <is>
           <t>https://aivillageblog.substack.com/p/season-2-recap-ai-organizes-event</t>
         </is>
       </c>
-      <c r="W38" s="19" t="n">
+      <c r="W38" s="21" t="n">
         <v>46321</v>
       </c>
       <c r="X38" s="5" t="n"/>
@@ -9168,7 +9616,7 @@
           <t>Influence-as-a-service: Claude used as the orchestrator deciding actions for 100+ social media bot personas</t>
         </is>
       </c>
-      <c r="D39" s="19" t="n">
+      <c r="D39" s="21" t="n">
         <v>45770</v>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -9199,7 +9647,7 @@
       <c r="J39" s="5" t="n"/>
       <c r="K39" s="5" t="inlineStr">
         <is>
-          <t>Emergent Agency</t>
+          <t>Multi-Agent Security</t>
         </is>
       </c>
       <c r="L39" s="5">
@@ -9225,19 +9673,23 @@
       <c r="R39" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="S39" s="5" t="n"/>
+      <c r="S39" s="5" t="inlineStr">
+        <is>
+          <t>Instance routing 2026-10-26: RF6 -&gt; RF7: an orchestrator directing 100+ personas is social engineering at scale, not emergent agency.</t>
+        </is>
+      </c>
       <c r="T39" s="5" t="n"/>
       <c r="U39" s="5" t="inlineStr">
         <is>
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V39" s="20" t="inlineStr">
+      <c r="V39" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2025-0027/</t>
         </is>
       </c>
-      <c r="W39" s="19" t="n">
+      <c r="W39" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X39" s="5" t="n"/>
@@ -9258,7 +9710,7 @@
           <t>Xanthorox AI: a self-hosted, five-model offensive platform sold on darknet forums for autonomous cyber operations</t>
         </is>
       </c>
-      <c r="D40" s="19" t="n">
+      <c r="D40" s="21" t="n">
         <v>45754</v>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -9323,12 +9775,12 @@
           <t>Agent Incident Registry (Enkrypt AI)</t>
         </is>
       </c>
-      <c r="V40" s="20" t="inlineStr">
+      <c r="V40" s="22" t="inlineStr">
         <is>
           <t>https://agentincident.vercel.app/i/AIR-2025-0019/</t>
         </is>
       </c>
-      <c r="W40" s="19" t="n">
+      <c r="W40" s="21" t="n">
         <v>46320</v>
       </c>
       <c r="X40" s="5" t="n"/>
@@ -9349,7 +9801,7 @@
           <t>False 'broken UI' belief spreads: Gemini 2.5 Pro logged its own misclicks as system bugs and its claims led other agents to doubt their own computers; nobody pushed back</t>
         </is>
       </c>
-      <c r="D41" s="21" t="n">
+      <c r="D41" s="23" t="n">
         <v>45748</v>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -9382,11 +9834,7 @@
           <t>Miscoordination</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>Information Asymmetries</t>
-        </is>
-      </c>
+      <c r="K41" s="5" t="n"/>
       <c r="L41" s="5">
         <f>IF(M41&gt;=9,"Strong",IF(M41&gt;=6,"Moderate",IF(M41&gt;=3,"Limited","Weak")))</f>
         <v/>
@@ -9412,7 +9860,7 @@
       </c>
       <c r="S41" s="5" t="inlineStr">
         <is>
-          <t>Verified. Apr–Jun 2025 (merch store goal). Also described in the Persuasion post (aivillageblog.substack.com/p/persuasion-in-the-ai-village-deepseek).</t>
+          <t>Verified. Apr–Jun 2025 (merch store goal). Also described in the Persuasion post (aivillageblog.substack.com/p/persuasion-in-the-ai-village-deepseek). Instance routing 2026-10-26: RF1 dropped: an agent misreading its own tooling is error, not deception, bargaining or a communication constraint.</t>
         </is>
       </c>
       <c r="T41" s="5" t="n"/>
@@ -9421,12 +9869,12 @@
           <t>What did we learn from the AI Village in 2025?</t>
         </is>
       </c>
-      <c r="V41" s="20" t="inlineStr">
+      <c r="V41" s="22" t="inlineStr">
         <is>
           <t>https://aivillageblog.substack.com/p/what-we-learned-2025</t>
         </is>
       </c>
-      <c r="W41" s="19" t="n">
+      <c r="W41" s="21" t="n">
         <v>46321</v>
       </c>
       <c r="X41" s="5" t="n"/>
@@ -9532,7 +9980,7 @@
           <t>Primary: operator report</t>
         </is>
       </c>
-      <c r="D2" s="20" t="inlineStr">
+      <c r="D2" s="22" t="inlineStr">
         <is>
           <t>https://cdn.openai.com/pdf/67869394-cb91-4c12-888c-5cbd85c7814c/OpenAI-Hugging-Face%20Incident-Technical-Report.pdf</t>
         </is>
@@ -9554,7 +10002,7 @@
           <t>Primary: operator report</t>
         </is>
       </c>
-      <c r="D3" s="20" t="inlineStr">
+      <c r="D3" s="22" t="inlineStr">
         <is>
           <t>https://openai.com/index/hugging-face-model-evaluation-security-incident/</t>
         </is>
@@ -9576,7 +10024,7 @@
           <t>Primary: operator report</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="22" t="inlineStr">
         <is>
           <t>https://openai.com/index/hugging-face-incident-and-the-road-ahead/</t>
         </is>
@@ -9598,7 +10046,7 @@
           <t>Primary: victim disclosure</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>https://huggingface.co/blog/security-incident-july-2026</t>
         </is>
@@ -9620,7 +10068,7 @@
           <t>Primary: victim disclosure</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>https://huggingface.co/blog/agent-intrusion-technical-timeline</t>
         </is>
@@ -9642,7 +10090,7 @@
           <t>Independent investigation</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>https://metr.org/blog/2026-08-26-openai-hugging-face-incident-investigation/</t>
         </is>
@@ -9664,7 +10112,7 @@
           <t>Secondary: forum summary</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>https://www.alignmentforum.org/posts/nB8KKapnWGBXtKKiM/brief-independent-investigation-of-agents-behavior-reasoning</t>
         </is>
@@ -9686,7 +10134,7 @@
           <t>Secondary: forum summary</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>https://www.lesswrong.com/posts/Khmh3ghqaGEpmpC9r/openai-offers-straight-laced-postmortem-of-the-huggingface</t>
         </is>
@@ -9708,7 +10156,7 @@
           <t>Independent investigation</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>https://www.kennethdegraff.com/swarm</t>
         </is>
@@ -9730,7 +10178,7 @@
           <t>Independent investigation</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>https://www.rubyhack.ai/</t>
         </is>
@@ -9752,7 +10200,7 @@
           <t>News</t>
         </is>
       </c>
-      <c r="D12" s="20" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>https://www.reuters.com/business/its-ai-agent-spent-days-hacking-company-sources-say-openai-did-not-notice-week-2026-07-24/</t>
         </is>
@@ -9774,7 +10222,7 @@
           <t>Secondary: forum summary</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>https://www.lesswrong.com/posts/jDeggMA22t3jGbTw6/36-000-ai-agents-are-now-speedrunning-civilization</t>
         </is>
@@ -9796,7 +10244,7 @@
           <t>Dataset</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>https://www.lesswrong.com/posts/WyrxmTwYbrwsT72sD/moltbook-data-repository</t>
         </is>
@@ -9818,7 +10266,7 @@
           <t>Primary: operator talk</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>https://www.youtube.com/watch?v=87DyyMV0kCY</t>
         </is>
@@ -9840,7 +10288,7 @@
           <t>Independent investigation</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>https://collusion.wiki/</t>
         </is>
@@ -9862,7 +10310,7 @@
           <t>Primary: operator statement</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>https://x.com/OpenAI/status/2096133504417616165</t>
         </is>
@@ -9880,7 +10328,7 @@
           <t>Primary: operator report</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>https://www.anthropic.com/news/investigating-incidents-cybersecurity-evals</t>
         </is>
@@ -9898,7 +10346,7 @@
           <t>Primary: government evaluator</t>
         </is>
       </c>
-      <c r="D19" s="20" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>https://www.aisi.gov.uk/blog/incident-report-unsanctioned-agent-behaviour-during-cyber-testing</t>
         </is>
@@ -9916,7 +10364,7 @@
           <t>Secondary: forum summary</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>https://www.lesswrong.com/posts/9it8pQRTz3orkZDty/my-short-summary-of-the-openai-agent-swarm-incidents</t>
         </is>
@@ -9934,7 +10382,7 @@
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D21" s="20" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>https://www.alignmentforum.org/posts/8oFYZdXkTaNGRtcn8/ai-swarms-are-starting-to-pose-indirect-takeover-risk</t>
         </is>
@@ -9952,7 +10400,7 @@
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>https://www.lesswrong.com/posts/Q65SETuTmhF4LWdix/detecting-collusion-through-multi-agent-interpretability-3</t>
         </is>
@@ -9970,7 +10418,7 @@
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>https://www.alignmentforum.org/posts/smMdYezaC8vuiLjCf/secret-collusion-will-we-know-when-to-unplug-ai</t>
         </is>
@@ -9992,7 +10440,7 @@
           <t>Primary: operator blog</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>https://aivillageblog.substack.com/p/what-we-learned-2025</t>
         </is>
@@ -10014,7 +10462,7 @@
           <t>Primary: operator blog</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>https://aivillageblog.substack.com/p/persuasion-in-the-ai-village-deepseek</t>
         </is>
@@ -10036,7 +10484,7 @@
           <t>Primary: operator blog</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>https://aivillageblog.substack.com/p/what-we-learned-2025</t>
         </is>
@@ -10058,7 +10506,7 @@
           <t>Primary: operator post</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
+      <c r="D27" s="22" t="inlineStr">
         <is>
           <t>https://x.com/aidigest_/status/2013673155198439507</t>
         </is>
@@ -10080,7 +10528,7 @@
           <t>Primary: operator blog</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="22" t="inlineStr">
         <is>
           <t>https://aivillageblog.substack.com/p/ai-village-reacts-to-huggingface</t>
         </is>
@@ -10102,7 +10550,7 @@
           <t>Dataset</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
+      <c r="D29" s="22" t="inlineStr">
         <is>
           <t>https://swarmtraces.org</t>
         </is>
@@ -10124,7 +10572,7 @@
           <t>Analysis</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
+      <c r="D30" s="22" t="inlineStr">
         <is>
           <t>https://incidentdatabase.ai/cite/1646/</t>
         </is>
@@ -10146,7 +10594,7 @@
           <t>News</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
+      <c r="D31" s="22" t="inlineStr">
         <is>
           <t>https://csoonline.com/article/4209210/ai-agents-wage-near-autonomous-cyberattack-on-asian-government-networks.html</t>
         </is>
@@ -10203,163 +10651,163 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="24" t="inlineStr">
         <is>
           <t>SOURCE</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="23" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Hammond et al. (2025). Multi-Agent Risks from Advanced AI. Cooperative AI Foundation Technical Report #1. arXiv:2502.14143.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>Instances and directions: paper Table 1. Case-study tags and hammond_type: paper Table 3.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="23" t="inlineStr"/>
+      <c r="A4" s="25" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>METHOD</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="23" t="inlineStr">
+      <c r="A6" s="25" t="inlineStr">
         <is>
           <t>Source of truth is data/*.csv in the repo; this file is generated by build/build_xlsx.py. Do not edit by hand.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Methodology, definitions and the evidence rubric: docs/methodology.md.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="23" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>TYPE: Observed in real world = deployed systems acting on real stakes outside experimenter control. Synthetic evidence = agents interacting in a simulated or researcher-built environment (e.g. GovSim, wargames, AI Village). Observed in lab = controlled experiment on real models in a narrow task probe. Theoretical = argument, formal model or non-AI analogue only.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="23" t="inlineStr">
+      <c r="A9" s="25" t="inlineStr">
         <is>
           <t>EVIDENCE SCORE: E1 ecological validity, E2 causal attribution, E3 scale and precision, E4 independent corroboration, E5 source vetting; each 0-2, summed 0-10. Bands: Strong 9-10, Moderate 6-8, Limited 3-5, Weak 0-2.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="23" t="inlineStr"/>
+      <c r="A10" s="25" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>EVIDENCE SHEET</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="23" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>One table for all evidence. evidence_class = Case study (Hammond et al. 2025 Table 3, shaded grey, CS ids) or Incident (the inventory, AIR/LW/AIV ids). Inclusion test for incidents: the behaviour arises from interaction between two or more AI agents, including one agent acting on another.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="23" t="inlineStr">
+      <c r="A13" s="25" t="inlineStr">
         <is>
           <t>id prefixes are listed in data/id_prefixes.csv. date: event date, or publication date for studies; partial dates show as yyyy or yyyy-mm. source_class: the source collection's own label, i.e. Hammond type for case studies, AIR class or main-source type for incidents.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>AIR class to type: In the wild and Safety failure -&gt; Observed in real world; Research demo and Disclosed vulnerability -&gt; Observed in lab.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>evidence_strength reads 'unscored' where E1-E5 are blank, i.e. rows held back pending a scope decision.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="23" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>The Sources sheet lists further sources per event; rows without event_id are leads not yet in the inventory. AIR asks users to contact Enkrypt AI before reusing its dataset.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="23" t="inlineStr"/>
+      <c r="A17" s="25" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="22" t="inlineStr">
+      <c r="A18" s="24" t="inlineStr">
         <is>
           <t>GROUNDING</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>grounding_score and evidence_score_max = highest evidence_score across the whole evidence inventory tagged with that risk, case studies and incidents alike (0 = none). Max, not sum or mean: corroboration is already scored inside each row as E4, and summing would let many weak rows outrank one strong one.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>evidence_n counts the rows behind the score. A high grounding on evidence_n = 1 rests on a single piece of evidence; read the two together.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Evidence tagged with a risk factor but no failure mode counts only towards that risk factor. Rows with blank E1-E5 are ignored by the score.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Instances: evidence_explicit and evidence_placement hold Hammond case-study ids only. Incidents attach directly to failure modes and risk factors, not to instances, because Table 1's sub-topics are finer-grained than this project's scope. Instance-level evidence stays as the paper records it.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="23" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>case_studies_explicit = the paper cross-references the case study in that instance's paragraph; case_studies_placement = the case-study box sits in that instance's discussion without an explicit reference.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="23" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>evidence_basis: Case study / Cited empirical work (no case study, but empirical studies cited) / Theoretical.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>Formulas need a spreadsheet app to compute (Excel 2019+ or LibreOffice). out/risk_index.csv has the same values precomputed.</t>
         </is>
